--- a/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
+++ b/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\bldgs\BCEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\90. 개인 폴더\김효진\기타업무\EPS\확인요청_빌딩\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3C5792-18E8-4F45-88C0-067B1418A7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6311DAEA-9FC6-43EE-B9A2-91A0CDC8BEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="705" windowWidth="13455" windowHeight="19980" tabRatio="952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1110" yWindow="5085" windowWidth="30240" windowHeight="15240" tabRatio="952" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -197,9 +197,6 @@
   <si>
     <t>Urban population rate</t>
     <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.index.go.kr/potal/main/EachDtlPageDetail.do?idx_cd=1200</t>
   </si>
   <si>
     <t>heating</t>
@@ -586,6 +583,10 @@
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
+  <si>
+    <t>https://www.index.go.kr/potal/main/EachDtlPageDetail.do?idx_cd=1200</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -599,7 +600,7 @@
     <numFmt numFmtId="180" formatCode="0.E+00"/>
     <numFmt numFmtId="181" formatCode="0.0.E+00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -752,8 +753,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -779,6 +788,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2ECF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -973,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1044,6 +1059,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="19" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="19" fillId="6" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="18" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="18" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1077,6 +1104,2407 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>초기값 변경 후</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$1:$AG$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2038</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2039</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2041</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2042</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2043</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2046</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2047</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2049</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>electricity (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$2:$AG$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>129000000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>128085531122407</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>129221921053730.27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>130255696422160.11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>131297741993537.39</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>132348123929485.69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>133406908920921.58</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>134474164192288.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>135549957505827.27</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>136634357165873.89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>137727432023200.88</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>138829251479386.48</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>139939885491221.58</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>141059404575151.34</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>142187879811752.56</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>143325382850246.59</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>144471985913048.56</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>145627761800352.94</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>146792783894755.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>147967126165913.81</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>149150863175241.13</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>150344070080643.06</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>151546822641288.22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>152759197222418.53</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>153981270800197.88</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>155213120966599.47</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>156454825934332.25</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>157706464541806.91</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>158968116258141.38</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>160239861188206.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>161521780077712.16</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>162813954318333.84</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>coal (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$3:$AG$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>natural gas (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$4:$AG$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>59200000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58150486891512.766</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57974902110890.578</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59134400153108.391</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60317088156170.563</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61523429919293.977</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>62753898517679.859</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>64008976488033.461</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>65289156017794.133</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>66594939138150.016</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67926837920913.016</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>69285374679331.273</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70671082172917.906</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>72084503816376.266</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>73526193892703.797</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>74996717770557.875</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>76496652125969.031</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>78026585168488.406</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>79587116871858.172</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>81178859209295.344</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>82802436393481.25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>84458485121350.875</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>86147654823777.891</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>87870607920253.453</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>89628020078658.531</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>91420580480231.703</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>93248992089836.344</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>95113971931633.078</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>97016251370265.734</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>98956576397671.047</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>100935707925624.47</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>102954422084136.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>petroleum diesel (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$5:$AG$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>1740000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1635011946079.1394</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1609349044937.332</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1532100290780.3401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1458559476822.8838</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1388548621935.3853</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1321898288082.4868</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1258447170254.5273</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1198041706082.3101</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1140535704190.3591</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1085789990389.2218</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1033672070850.5391</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>984055811449.71313</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>936821132500.12683</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>891853718140.12073</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>849044739669.3949</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>808290592165.26392</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>769492643741.33118</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>732556996841.74719</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>697394260993.34326</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>663919336465.66272</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>632051208315.31091</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>601712750316.1759</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>572830538300.99939</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>545334672462.55139</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>519158608184.34888</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>494238994991.50012</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>470515523231.90808</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>447930778116.77649</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>426430100767.1712</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>405961455930.34698</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>386475306045.69031</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>heat (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$6:$AG$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>15100000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14511153872761.668</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14617592654224.467</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14880709322000.508</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15148562089796.518</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15421236207412.855</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15698818459146.287</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15981397191410.92</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16269062340856.316</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16561905462991.73</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16860019761325.582</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17163500117029.443</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17472443119135.973</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17786947095280.422</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18107112142995.469</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18433040161569.387</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18764834884477.637</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19102601912398.234</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19446448746821.402</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19796484824264.188</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20152821551100.941</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20515572339020.758</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20884852641123.133</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21260779988663.348</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21643474028459.289</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>22033056560971.555</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>22429651579069.043</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>22833385307492.285</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>23244386243027.148</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>23662785195401.637</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>24088715328918.867</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>24522312204839.406</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>biomass (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$7:$AG$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>6267151983000.002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6688080101261.1963</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7174485926807.4648</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7497337793513.7998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7834717994221.9199</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8187280303961.9063</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8555707917640.1914</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8940714773934</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9343046938761.0293</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9763484051005.2754</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10202840833300.512</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10661968670799.033</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11141757260984.988</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11643136337729.313</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12167077472927.131</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12714595959208.852</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13286752777373.248</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13884656652355.043</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14509466201711.02</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>15162392180788.014</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15844699828923.473</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16557711321225.027</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17302808330680.152</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>18081434705560.758</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>18895099267310.992</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>19745378734339.984</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>20633920777385.281</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>21562447212367.617</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22532757336924.16</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>23546731417085.746</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>24606334330854.602</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>25713619375743.059</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>kerosene (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$8:$AG$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>31500000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29616860228748.609</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29151998453271.219</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27752702527514.199</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26420572806193.516</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25152385311496.227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23945070816544.406</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22795707417350.273</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21701513461317.461</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20659840815174.223</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19668168456045.859</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>18724096370155.656</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17825339744388.184</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16969723436657.551</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16155176711697.988</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15379728229536.484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14641501274518.732</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13938709213341.832</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>13269651171101.424</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12632707914888.555</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12026337934973.904</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11449073714095.156</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10899518175818.588</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10376341303379.295</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9878276920817.0879</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9404119628617.8672</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8952721886444.209</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8522991235894.8867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8113887656571.9316</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7724421049056.4785</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7353648838701.7676</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7000673694444.082</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>heavy or residual fuel oil (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$9:$AG$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>3900000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3658245906752.4121</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3600826630225.0806</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3427986951974.2764</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3263443578279.5107</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3106798286522.0942</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2957671968769.0337</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2815703714268.1201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2680549935983.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2551883539056.0537</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2429393129181.3628</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2312782258980.6572</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2201768710549.5854</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2096083812443.2053</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1995471789445.9314</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1899689143552.5266</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1808504064662.0054</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1721695869558.229</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1639054467819.4338</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1560379853364.1008</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1485481620402.624</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1414178502623.2981</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1346297934497.3796</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1281675633641.5054</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1220155203226.7131</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1161587753471.8308</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1105831541305.1829</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1052751627322.5341</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1002219549211.0524</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>954113010848.92175</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>908315586328.17346</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>864716438184.42114</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LPG propane or butane (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$10:$AG$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>19000000000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17835815247411.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17555866978791.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16713185363809.279</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15910952466346.434</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15147226747961.805</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14420159864059.637</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13727992190584.773</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13069048565436.703</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12441734234295.74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11844530991049.545</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11275993503479.166</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10734745815312.166</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10219478016177.182</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9728943071400.6758</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9261953803973.4434</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8817380021382.7168</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8394145780356.3457</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7991226782899.2412</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7607647897320.0771</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7242480798248.7129</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6894841719932.7744</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6563889317376.001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6248822630141.9531</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5948879143895.1387</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5663332944988.1719</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5391492963628.7393</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5132701301374.5596</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4886331638908.5801</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4651787720240.9678</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4428501909669.4014</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4215933818005.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'BCEU-commercial-heating'!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>hydrogen (BTU)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'BCEU-commercial-heating'!$B$11:$AG$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-13A1-41AA-A13C-6A3D4F91CF22}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="558921519"/>
+        <c:axId val="558922959"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="558921519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="558922959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="558922959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="558921519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1411100</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>15689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>104215</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>91889</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A5E4BC0-2CF2-A2B6-EDAB-E07F67358918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1481,14 +3909,14 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="10"/>
     </row>
@@ -1511,7 +3939,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -1585,7 +4013,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" s="10">
         <v>39.683100000000003</v>
@@ -1653,8 +4081,8 @@
       <c r="B37" s="14">
         <v>0.91800000000000004</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>36</v>
+      <c r="C37" s="33" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1694,9 +4122,10 @@
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{E3D81ACC-CD3F-44CE-83E2-D8AE4FA810A2}"/>
     <hyperlink ref="B14" r:id="rId2" xr:uid="{33897A44-3821-4B6E-8927-AA2917681289}"/>
+    <hyperlink ref="C37" r:id="rId3" xr:uid="{7D2E10FF-A52A-4B4D-B3F1-4EB000345C4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -1711,12 +4140,12 @@
   <sheetData>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1">
         <v>2019</v>
@@ -3169,7 +5598,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -4622,7 +7051,7 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>2019</v>
@@ -6075,7 +8504,7 @@
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1">
         <v>2019</v>
@@ -7528,7 +9957,7 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="1">
         <v>2019</v>
@@ -8981,7 +11410,7 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1">
         <v>2019</v>
@@ -23541,44 +25970,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED6D3F1-92E7-40E9-A07E-C7DBA9C24A0B}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36">
+      <c r="B2" s="44">
         <v>129000000000000</v>
       </c>
       <c r="C2" s="36">
@@ -23597,11 +26027,11 @@
         <v>68100000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="44">
         <v>0</v>
       </c>
       <c r="C3" s="36">
@@ -23619,12 +26049,14 @@
       <c r="G3" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3" s="36"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="44">
         <v>59200000000000</v>
       </c>
       <c r="C4" s="36">
@@ -23642,12 +26074,14 @@
       <c r="G4" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4" s="36"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="44">
         <v>1740000000000</v>
       </c>
       <c r="C5" s="36">
@@ -23666,11 +26100,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="44">
         <v>15100000000000</v>
       </c>
       <c r="C6" s="36">
@@ -23689,12 +26123,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="36">
-        <v>42700000000000</v>
+      <c r="B7" s="45">
+        <v>6267151983000.002</v>
       </c>
       <c r="C7" s="36">
         <v>208000000000</v>
@@ -23711,12 +26145,13 @@
       <c r="G7" s="36">
         <v>139000000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="44">
         <v>31500000000000</v>
       </c>
       <c r="C8" s="36">
@@ -23735,11 +26170,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="44">
         <v>3900000000000</v>
       </c>
       <c r="C9" s="36">
@@ -23758,11 +26193,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="44">
         <v>19000000000000</v>
       </c>
       <c r="C10" s="36">
@@ -23781,11 +26216,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="44">
         <v>0</v>
       </c>
       <c r="C11" s="36">
@@ -23804,33 +26239,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -23853,7 +26288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -23876,7 +26311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>4</v>
       </c>
@@ -24062,25 +26497,25 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -25781,10 +28216,10 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
-    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="32" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="32" width="10.25" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26556,137 +28991,137 @@
         <v>24522312204839.406</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:35" s="40" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="39">
         <f>Commercial_calculation!B9</f>
-        <v>42700000000000</v>
-      </c>
-      <c r="C7" s="3">
+        <v>6267151983000.002</v>
+      </c>
+      <c r="C7" s="39">
         <f>Commercial_calculation!C9</f>
-        <v>45560446860313.336</v>
-      </c>
-      <c r="D7" s="3">
+        <v>6688080101261.1963</v>
+      </c>
+      <c r="D7" s="39">
         <f>Commercial_calculation!D9</f>
-        <v>48873933904699.766</v>
-      </c>
-      <c r="E7" s="3">
+        <v>7174485926807.4648</v>
+      </c>
+      <c r="E7" s="39">
         <f>Commercial_calculation!E9</f>
-        <v>51073260930411.25</v>
-      </c>
-      <c r="F7" s="3">
+        <v>7497337793513.7998</v>
+      </c>
+      <c r="F7" s="39">
         <f>Commercial_calculation!F9</f>
-        <v>53371557672279.75</v>
-      </c>
-      <c r="G7" s="3">
+        <v>7834717994221.9199</v>
+      </c>
+      <c r="G7" s="39">
         <f>Commercial_calculation!G9</f>
-        <v>55773277767532.336</v>
-      </c>
-      <c r="H7" s="3">
+        <v>8187280303961.9063</v>
+      </c>
+      <c r="H7" s="39">
         <f>Commercial_calculation!H9</f>
-        <v>58283075267071.289</v>
-      </c>
-      <c r="I7" s="3">
+        <v>8555707917640.1914</v>
+      </c>
+      <c r="I7" s="39">
         <f>Commercial_calculation!I9</f>
-        <v>60905813654089.492</v>
-      </c>
-      <c r="J7" s="3">
+        <v>8940714773934</v>
+      </c>
+      <c r="J7" s="39">
         <f>Commercial_calculation!J9</f>
-        <v>63646575268523.516</v>
-      </c>
-      <c r="K7" s="3">
+        <v>9343046938761.0293</v>
+      </c>
+      <c r="K7" s="39">
         <f>Commercial_calculation!K9</f>
-        <v>66510671155607.07</v>
-      </c>
-      <c r="L7" s="3">
+        <v>9763484051005.2754</v>
+      </c>
+      <c r="L7" s="39">
         <f>Commercial_calculation!L9</f>
-        <v>69503651357609.383</v>
-      </c>
-      <c r="M7" s="3">
+        <v>10202840833300.512</v>
+      </c>
+      <c r="M7" s="39">
         <f>Commercial_calculation!M9</f>
-        <v>72631315668701.797</v>
-      </c>
-      <c r="N7" s="3">
+        <v>10661968670799.033</v>
+      </c>
+      <c r="N7" s="39">
         <f>Commercial_calculation!N9</f>
-        <v>75899724873793.375</v>
-      </c>
-      <c r="O7" s="3">
+        <v>11141757260984.988</v>
+      </c>
+      <c r="O7" s="39">
         <f>Commercial_calculation!O9</f>
-        <v>79315212493114.078</v>
-      </c>
-      <c r="P7" s="3">
+        <v>11643136337729.313</v>
+      </c>
+      <c r="P7" s="39">
         <f>Commercial_calculation!P9</f>
-        <v>82884397055304.203</v>
-      </c>
-      <c r="Q7" s="3">
+        <v>12167077472927.131</v>
+      </c>
+      <c r="Q7" s="39">
         <f>Commercial_calculation!Q9</f>
-        <v>86614194922792.891</v>
-      </c>
-      <c r="R7" s="3">
+        <v>12714595959208.852</v>
+      </c>
+      <c r="R7" s="39">
         <f>Commercial_calculation!R9</f>
-        <v>90511833694318.563</v>
-      </c>
-      <c r="S7" s="3">
+        <v>13286752777373.248</v>
+      </c>
+      <c r="S7" s="39">
         <f>Commercial_calculation!S9</f>
-        <v>94584866210562.891</v>
-      </c>
-      <c r="T7" s="3">
+        <v>13884656652355.043</v>
+      </c>
+      <c r="T7" s="39">
         <f>Commercial_calculation!T9</f>
-        <v>98841185190038.219</v>
-      </c>
-      <c r="U7" s="3">
+        <v>14509466201711.02</v>
+      </c>
+      <c r="U7" s="39">
         <f>Commercial_calculation!U9</f>
-        <v>103289038523589.94</v>
-      </c>
-      <c r="V7" s="3">
+        <v>15162392180788.014</v>
+      </c>
+      <c r="V7" s="39">
         <f>Commercial_calculation!V9</f>
-        <v>107937045257151.48</v>
-      </c>
-      <c r="W7" s="3">
+        <v>15844699828923.473</v>
+      </c>
+      <c r="W7" s="39">
         <f>Commercial_calculation!W9</f>
-        <v>112794212293723.3</v>
-      </c>
-      <c r="X7" s="3">
+        <v>16557711321225.027</v>
+      </c>
+      <c r="X7" s="39">
         <f>Commercial_calculation!X9</f>
-        <v>117869951846940.84</v>
-      </c>
-      <c r="Y7" s="3">
+        <v>17302808330680.152</v>
+      </c>
+      <c r="Y7" s="39">
         <f>Commercial_calculation!Y9</f>
-        <v>123174099680053.17</v>
-      </c>
-      <c r="Z7" s="3">
+        <v>18081434705560.758</v>
+      </c>
+      <c r="Z7" s="39">
         <f>Commercial_calculation!Z9</f>
-        <v>128716934165655.56</v>
-      </c>
-      <c r="AA7" s="3">
+        <v>18895099267310.992</v>
+      </c>
+      <c r="AA7" s="39">
         <f>Commercial_calculation!AA9</f>
-        <v>134509196203110.05</v>
-      </c>
-      <c r="AB7" s="3">
+        <v>19745378734339.984</v>
+      </c>
+      <c r="AB7" s="39">
         <f>Commercial_calculation!AB9</f>
-        <v>140562110032249.98</v>
-      </c>
-      <c r="AC7" s="3">
+        <v>20633920777385.281</v>
+      </c>
+      <c r="AC7" s="39">
         <f>Commercial_calculation!AC9</f>
-        <v>146887404983701.22</v>
-      </c>
-      <c r="AD7" s="3">
+        <v>21562447212367.617</v>
+      </c>
+      <c r="AD7" s="39">
         <f>Commercial_calculation!AD9</f>
-        <v>153497338207967.75</v>
-      </c>
-      <c r="AE7" s="3">
+        <v>22532757336924.16</v>
+      </c>
+      <c r="AE7" s="39">
         <f>Commercial_calculation!AE9</f>
-        <v>160404718427326.28</v>
-      </c>
-      <c r="AF7" s="3">
+        <v>23546731417085.746</v>
+      </c>
+      <c r="AF7" s="39">
         <f>Commercial_calculation!AF9</f>
-        <v>167622930756555.94</v>
-      </c>
-      <c r="AG7" s="3">
+        <v>24606334330854.602</v>
+      </c>
+      <c r="AG7" s="39">
         <f>Commercial_calculation!AG9</f>
-        <v>175165962640600.94</v>
+        <v>25713619375743.059</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
@@ -27225,6 +29660,7 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -34180,46 +36616,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="I1" s="16">
         <v>2020</v>
       </c>
       <c r="J1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -34251,7 +36687,7 @@
         <v>67518903420123.07</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" s="2">
         <v>128085531122407</v>
@@ -34301,7 +36737,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -34351,7 +36787,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J4" s="2">
         <v>58150486891512.766</v>
@@ -34401,7 +36837,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J5" s="2">
         <v>1635011946079.1394</v>
@@ -34451,7 +36887,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J6" s="2">
         <v>14511153872761.668</v>
@@ -34476,9 +36912,9 @@
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="43">
         <f t="shared" si="5"/>
-        <v>45560446860313.336</v>
+        <v>6688080101261.1963</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
@@ -34501,10 +36937,10 @@
         <v>148164054830.28726</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45560446860313.336</v>
+        <v>119</v>
+      </c>
+      <c r="J7" s="43">
+        <v>6688080101261.1963</v>
       </c>
       <c r="K7" s="2">
         <v>222246082245.43088</v>
@@ -34551,7 +36987,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J8" s="2">
         <v>29616860228748.609</v>
@@ -34601,7 +37037,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J9" s="2">
         <v>3658245906752.4121</v>
@@ -34651,7 +37087,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2">
         <v>17835815247411.25</v>
@@ -34701,7 +37137,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -34727,46 +37163,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I13" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="N13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="O13" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -34798,7 +37234,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J14" s="2">
         <v>17595574230689.395</v>
@@ -34844,7 +37280,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" s="2">
         <v>11428732800000.002</v>
@@ -34884,7 +37320,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J16" s="2">
         <v>339009213195426.94</v>
@@ -34926,7 +37362,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -34964,7 +37400,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J18" s="2">
         <v>86945672100000.016</v>
@@ -35004,7 +37440,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J19" s="2">
         <v>18214542900000</v>
@@ -35044,7 +37480,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -35082,7 +37518,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21" s="2">
         <v>87546310183815.938</v>
@@ -35122,7 +37558,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J22" s="2">
         <v>22005720583502.262</v>
@@ -35164,7 +37600,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -35175,25 +37611,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -35504,46 +37940,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="I1" s="16">
         <v>2021</v>
       </c>
       <c r="J1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -35575,7 +38011,7 @@
         <v>68119493654016.609</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" s="2">
         <v>129221921053730.27</v>
@@ -35625,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -35675,7 +38111,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J4" s="2">
         <v>57974902110890.578</v>
@@ -35725,7 +38161,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J5" s="2">
         <v>1609349044937.332</v>
@@ -35775,7 +38211,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J6" s="2">
         <v>14617592654224.467</v>
@@ -35802,7 +38238,7 @@
       </c>
       <c r="B7" s="2">
         <f t="shared" si="1"/>
-        <v>48873933904699.766</v>
+        <v>7174485926807.4648</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
@@ -35825,10 +38261,10 @@
         <v>158939622454.30817</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="2">
-        <v>48873933904699.766</v>
+        <v>119</v>
+      </c>
+      <c r="J7" s="43">
+        <v>7174485926807.4648</v>
       </c>
       <c r="K7" s="2">
         <v>238409433681.46222</v>
@@ -35875,7 +38311,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J8" s="2">
         <v>29151998453271.219</v>
@@ -35925,7 +38361,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J9" s="2">
         <v>3600826630225.0806</v>
@@ -35975,7 +38411,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2">
         <v>17555866978791.26</v>
@@ -36025,7 +38461,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -36051,46 +38487,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I13" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="N13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="O13" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -36122,7 +38558,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J14" s="2">
         <v>19482237708106.813</v>
@@ -36170,7 +38606,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" s="2">
         <v>7857253800000</v>
@@ -36210,7 +38646,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J16" s="2">
         <v>355852532026135.06</v>
@@ -36252,7 +38688,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -36290,7 +38726,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J18" s="2">
         <v>95429070691603.063</v>
@@ -36330,7 +38766,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J19" s="2">
         <v>26613557282608.699</v>
@@ -36370,7 +38806,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -36408,7 +38844,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21" s="2">
         <v>87387019904385.5</v>
@@ -36448,7 +38884,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J22" s="2">
         <v>21965681233203.488</v>
@@ -36490,7 +38926,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -36504,25 +38940,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="I25"/>
     </row>
@@ -36834,10 +39270,10 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -36922,15 +39358,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>127</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="37">
         <v>-0.01</v>
@@ -36938,7 +39374,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="37">
         <v>2.5000000000000001E-2</v>
@@ -36946,7 +39382,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
@@ -36954,7 +39390,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="37">
         <v>-6.0000000000000001E-3</v>
@@ -36962,7 +39398,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="37">
         <v>7.0000000000000001E-3</v>
@@ -36970,7 +39406,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="37">
         <v>-1.4E-2</v>
@@ -36978,10 +39414,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -37000,10 +39436,10 @@
         <v>-8.6999999999999994E-2</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -37034,7 +39470,7 @@
       <c r="A28" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="42">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
@@ -37092,31 +39528,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -37310,7 +39746,7 @@
       </c>
       <c r="B7" s="2">
         <f>Commercial_calculation!W9</f>
-        <v>112794212293723.3</v>
+        <v>16557711321225.027</v>
       </c>
       <c r="C7" s="2">
         <f>Commercial_calculation!W21</f>
@@ -37334,11 +39770,11 @@
       </c>
       <c r="I7" s="2">
         <f t="shared" si="0"/>
-        <v>140488401003239.09</v>
+        <v>44251900030740.813</v>
       </c>
       <c r="J7" s="18">
         <f>I7/10^6/About!$B$30/10^6</f>
-        <v>3.540257716842663</v>
+        <v>1.1151321351089207</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -37493,11 +39929,11 @@
       <c r="A12" s="16"/>
       <c r="I12" s="2">
         <f>SUM(I2:I11)</f>
-        <v>1078632810520066.5</v>
+        <v>982396309547568.13</v>
       </c>
       <c r="J12" s="18">
         <f>I12/10^6/About!$B$30/10^6</f>
-        <v>27.181163027083731</v>
+        <v>24.756037445349985</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -37506,31 +39942,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="E14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="G14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -37918,31 +40354,31 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D27" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="E27" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="F27" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="G27" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>42</v>
-      </c>
       <c r="I27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -38379,7 +40815,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -38400,126 +40836,126 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="F1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="G1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="K1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="L1" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="S1" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="T1" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="U1" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="V1" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="W1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="20" t="s">
+      <c r="X1" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="Y1" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="AA1" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB1" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AB1" s="20" t="s">
+      <c r="AC1" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AC1" s="20" t="s">
+      <c r="AD1" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AD1" s="20" t="s">
+      <c r="AE1" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AE1" s="20" t="s">
+      <c r="AF1" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AF1" s="20" t="s">
+      <c r="AG1" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="AG1" s="20" t="s">
+      <c r="AH1" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="AH1" s="20" t="s">
+      <c r="AI1" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="AI1" s="20" t="s">
+      <c r="AJ1" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="AJ1" s="20" t="s">
+      <c r="AK1" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="AK1" s="30" t="s">
+      <c r="AL1" s="30" t="s">
         <v>104</v>
-      </c>
-      <c r="AL1" s="30" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="C2" s="21">
         <v>3574</v>
@@ -38634,10 +41070,10 @@
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C3" s="21">
         <v>1976</v>
@@ -38752,10 +41188,10 @@
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="21">
         <v>46</v>
@@ -38870,10 +41306,10 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C5" s="21">
         <v>0</v>
@@ -38986,10 +41422,10 @@
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="21">
         <v>520</v>
@@ -39104,10 +41540,10 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C7" s="21">
         <v>230</v>
@@ -39222,10 +41658,10 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="21">
         <v>1996</v>
@@ -39340,10 +41776,10 @@
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C9" s="21">
         <v>486</v>
@@ -39458,10 +41894,10 @@
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="21">
         <v>537</v>
@@ -39576,10 +42012,10 @@
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C11" s="21">
         <v>1191</v>
@@ -39694,10 +42130,10 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="21">
         <v>436</v>
@@ -39812,10 +42248,10 @@
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C13" s="21">
         <v>55</v>
@@ -39930,10 +42366,10 @@
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="21">
         <v>40</v>
@@ -40048,10 +42484,10 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="C15" s="21">
         <v>14</v>
@@ -40166,10 +42602,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="C17" s="26">
         <v>2019</v>
@@ -40181,13 +42617,13 @@
         <v>2021</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="I17" s="29">
         <v>2019</v>
@@ -40199,15 +42635,15 @@
         <v>2021</v>
       </c>
       <c r="L17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="C18" s="18">
         <f>SUM(C2:N2)</f>
@@ -40222,10 +42658,10 @@
         <v>23704.455724820378</v>
       </c>
       <c r="G18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="I18" s="32">
         <f>C18*About!$B$30*10^9</f>
@@ -40242,10 +42678,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C19" s="18">
         <f>SUM(C3:N3)+B42</f>
@@ -40260,10 +42696,10 @@
         <v>22760.5431348325</v>
       </c>
       <c r="G19" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I19" s="32">
         <f>C19*About!$B$30*10^9</f>
@@ -40280,10 +42716,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="18">
         <f t="shared" ref="C20:D30" si="11">SUM(C4:N4)</f>
@@ -40298,10 +42734,10 @@
         <v>198</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I20" s="32">
         <f>C20*About!$B$30*10^9</f>
@@ -40318,10 +42754,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C21" s="18">
         <f t="shared" si="11"/>
@@ -40336,10 +42772,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I21" s="32">
         <f>C21*About!$B$30*10^9</f>
@@ -40356,10 +42792,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="18">
         <f t="shared" si="11"/>
@@ -40374,10 +42810,10 @@
         <v>2871.7653061224491</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I22" s="32">
         <f>C22*About!$B$30*10^9</f>
@@ -40394,10 +42830,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C23" s="18">
         <f>SUM(C7:N7)+B43</f>
@@ -40412,10 +42848,10 @@
         <v>2821.7816091954023</v>
       </c>
       <c r="G23" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I23" s="32">
         <f>C23*About!$B$30*10^9</f>
@@ -40432,10 +42868,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" s="18">
         <f t="shared" si="11"/>
@@ -40450,10 +42886,10 @@
         <v>10848.48368522073</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I24" s="32">
         <f>C24*About!$B$30*10^9</f>
@@ -40470,10 +42906,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C25" s="18">
         <f>SUM(C9:N9)+B44</f>
@@ -40488,10 +42924,10 @@
         <v>3632.3333333333335</v>
       </c>
       <c r="G25" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I25" s="32">
         <f>C25*About!$B$30*10^9</f>
@@ -40508,10 +42944,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="18">
         <f t="shared" si="11"/>
@@ -40526,10 +42962,10 @@
         <v>6709.7759336099589</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26" s="32">
         <f>C26*About!$B$30*10^9</f>
@@ -40546,10 +42982,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C27" s="18">
         <f>SUM(C11:N11)+B45</f>
@@ -40564,10 +43000,10 @@
         <v>14369.366336633662</v>
       </c>
       <c r="G27" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I27" s="32">
         <f>C27*About!$B$30*10^9</f>
@@ -40584,10 +43020,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" s="18">
         <f t="shared" si="11"/>
@@ -40602,10 +43038,10 @@
         <v>2404.7786259541986</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I28" s="32">
         <f>C28*About!$B$30*10^9</f>
@@ -40622,10 +43058,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="C29" s="18">
         <f>SUM(C13:N13)+B46</f>
@@ -40640,10 +43076,10 @@
         <v>412</v>
       </c>
       <c r="G29" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>84</v>
       </c>
       <c r="I29" s="32">
         <f>C29*About!$B$30*10^9</f>
@@ -40660,10 +43096,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="18">
         <f t="shared" si="11"/>
@@ -40678,10 +43114,10 @@
         <v>670.6521739130435</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I30" s="32">
         <f>C30*About!$B$30*10^9</f>
@@ -40698,10 +43134,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="C31" s="18">
         <f>SUM(C15:N15)+B47</f>
@@ -40716,10 +43152,10 @@
         <v>1534.0618556701031</v>
       </c>
       <c r="G31" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="I31" s="32">
         <f>C31*About!$B$30*10^9</f>
@@ -40736,120 +43172,120 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="D33" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="E33" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="F33" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="G33" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="H33" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="I33" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="J33" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="J33" s="20" t="s">
+      <c r="K33" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="L33" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="L33" s="20" t="s">
+      <c r="M33" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="M33" s="20" t="s">
+      <c r="N33" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="N33" s="20" t="s">
+      <c r="O33" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="O33" s="20" t="s">
+      <c r="P33" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="P33" s="20" t="s">
+      <c r="Q33" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="Q33" s="20" t="s">
+      <c r="R33" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="R33" s="20" t="s">
+      <c r="S33" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="S33" s="20" t="s">
+      <c r="T33" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="T33" s="20" t="s">
+      <c r="U33" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="20" t="s">
+      <c r="V33" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="V33" s="20" t="s">
+      <c r="W33" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="W33" s="20" t="s">
+      <c r="X33" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="X33" s="20" t="s">
+      <c r="Y33" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="Y33" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="Z33" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA33" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AA33" s="20" t="s">
+      <c r="AB33" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AB33" s="20" t="s">
+      <c r="AC33" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AC33" s="20" t="s">
+      <c r="AD33" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AD33" s="20" t="s">
+      <c r="AE33" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AE33" s="20" t="s">
+      <c r="AF33" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="AF33" s="20" t="s">
+      <c r="AG33" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="AG33" s="20" t="s">
+      <c r="AH33" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="AH33" s="20" t="s">
+      <c r="AI33" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="AI33" s="20" t="s">
+      <c r="AJ33" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="AJ33" s="30" t="s">
+      <c r="AK33" s="30" t="s">
         <v>104</v>
-      </c>
-      <c r="AK33" s="30" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="21">
         <v>579</v>
@@ -40964,7 +43400,7 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="21">
         <v>163</v>
@@ -41079,7 +43515,7 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="21">
         <v>14</v>
@@ -41194,7 +43630,7 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37" s="21">
         <v>271</v>
@@ -41309,7 +43745,7 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="21">
         <v>13</v>
@@ -41424,7 +43860,7 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39" s="21">
         <v>118</v>
@@ -41539,7 +43975,7 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="26">
         <v>2019</v>
@@ -41551,10 +43987,10 @@
         <v>2021</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H41" s="26">
         <v>2019</v>
@@ -41566,12 +44002,12 @@
         <v>2021</v>
       </c>
       <c r="K41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B42" s="27">
         <f t="shared" ref="B42:B47" si="14">SUM(B34:M34)</f>
@@ -41586,7 +44022,7 @@
         <v>5502.5431348325019</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" s="28">
         <f>B42*About!$B$30*10^9</f>
@@ -41603,7 +44039,7 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="27">
         <f t="shared" si="14"/>
@@ -41618,7 +44054,7 @@
         <v>1105.7816091954023</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H43" s="28">
         <f>B43*About!$B$30*10^9</f>
@@ -41635,7 +44071,7 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B44" s="27">
         <f t="shared" si="14"/>
@@ -41650,7 +44086,7 @@
         <v>90.333333333333343</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" s="28">
         <f>B44*About!$B$30*10^9</f>
@@ -41667,7 +44103,7 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B45" s="27">
         <f t="shared" si="14"/>
@@ -41682,7 +44118,7 @@
         <v>2842.3663366336632</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H45" s="28">
         <f>B45*About!$B$30*10^9</f>
@@ -41699,7 +44135,7 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" s="27">
         <f t="shared" si="14"/>
@@ -41714,7 +44150,7 @@
         <v>70</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H46" s="28">
         <f>B46*About!$B$30*10^9</f>
@@ -41731,7 +44167,7 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="27">
         <f t="shared" si="14"/>
@@ -41746,7 +44182,7 @@
         <v>1395.0618556701031</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H47" s="28">
         <f>B47*About!$B$30*10^9</f>
@@ -41779,12 +44215,16 @@
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="E2">
+        <f>1+Forecast!$B28</f>
+        <v>1.0449999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1">
         <v>2019</v>
@@ -42549,136 +44989,136 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2">
         <f>INDEX(SYCEU!$B$2:$G$11, MATCH($A9, SYCEU!$A$2:$A$11, 0), MATCH(Commercial_calculation!$A$3, SYCEU!$B$1:$G$1, 0))</f>
-        <v>42700000000000</v>
+        <v>6267151983000.002</v>
       </c>
       <c r="C9" s="2">
         <f>INDEX('2020'!$B$2:$G$11, MATCH($A9, '2020'!$A$2:$A$11, 0), MATCH(Commercial_calculation!$A$3, '2020'!$B$1:$G$1, 0))</f>
-        <v>45560446860313.336</v>
+        <v>6688080101261.1963</v>
       </c>
       <c r="D9" s="2">
         <f>INDEX('2021'!$B$2:$G$11, MATCH($A9, '2021'!$A$2:$A$11, 0), MATCH(Commercial_calculation!$A$3, '2021'!$B$1:$G$1, 0))</f>
-        <v>48873933904699.766</v>
+        <v>7174485926807.4648</v>
       </c>
       <c r="E9" s="2">
         <f>MAX(0,D9*(1+Forecast!$B28))</f>
-        <v>51073260930411.25</v>
+        <v>7497337793513.7998</v>
       </c>
       <c r="F9" s="2">
         <f>MAX(0,E9*(1+Forecast!$B28))</f>
-        <v>53371557672279.75</v>
+        <v>7834717994221.9199</v>
       </c>
       <c r="G9" s="2">
         <f>MAX(0,F9*(1+Forecast!$B28))</f>
-        <v>55773277767532.336</v>
+        <v>8187280303961.9063</v>
       </c>
       <c r="H9" s="2">
         <f>MAX(0,G9*(1+Forecast!$B28))</f>
-        <v>58283075267071.289</v>
+        <v>8555707917640.1914</v>
       </c>
       <c r="I9" s="2">
         <f>MAX(0,H9*(1+Forecast!$B28))</f>
-        <v>60905813654089.492</v>
+        <v>8940714773934</v>
       </c>
       <c r="J9" s="2">
         <f>MAX(0,I9*(1+Forecast!$B28))</f>
-        <v>63646575268523.516</v>
+        <v>9343046938761.0293</v>
       </c>
       <c r="K9" s="2">
         <f>MAX(0,J9*(1+Forecast!$B28))</f>
-        <v>66510671155607.07</v>
+        <v>9763484051005.2754</v>
       </c>
       <c r="L9" s="2">
         <f>MAX(0,K9*(1+Forecast!$B28))</f>
-        <v>69503651357609.383</v>
+        <v>10202840833300.512</v>
       </c>
       <c r="M9" s="2">
         <f>MAX(0,L9*(1+Forecast!$B28))</f>
-        <v>72631315668701.797</v>
+        <v>10661968670799.033</v>
       </c>
       <c r="N9" s="2">
         <f>MAX(0,M9*(1+Forecast!$B28))</f>
-        <v>75899724873793.375</v>
+        <v>11141757260984.988</v>
       </c>
       <c r="O9" s="2">
         <f>MAX(0,N9*(1+Forecast!$B28))</f>
-        <v>79315212493114.078</v>
+        <v>11643136337729.313</v>
       </c>
       <c r="P9" s="2">
         <f>MAX(0,O9*(1+Forecast!$B28))</f>
-        <v>82884397055304.203</v>
+        <v>12167077472927.131</v>
       </c>
       <c r="Q9" s="2">
         <f>MAX(0,P9*(1+Forecast!$B28))</f>
-        <v>86614194922792.891</v>
+        <v>12714595959208.852</v>
       </c>
       <c r="R9" s="2">
         <f>MAX(0,Q9*(1+Forecast!$B28))</f>
-        <v>90511833694318.563</v>
+        <v>13286752777373.248</v>
       </c>
       <c r="S9" s="2">
         <f>MAX(0,R9*(1+Forecast!$B28))</f>
-        <v>94584866210562.891</v>
+        <v>13884656652355.043</v>
       </c>
       <c r="T9" s="2">
         <f>MAX(0,S9*(1+Forecast!$B28))</f>
-        <v>98841185190038.219</v>
+        <v>14509466201711.02</v>
       </c>
       <c r="U9" s="2">
         <f>MAX(0,T9*(1+Forecast!$B28))</f>
-        <v>103289038523589.94</v>
+        <v>15162392180788.014</v>
       </c>
       <c r="V9" s="2">
         <f>MAX(0,U9*(1+Forecast!$B28))</f>
-        <v>107937045257151.48</v>
+        <v>15844699828923.473</v>
       </c>
       <c r="W9" s="2">
         <f>MAX(0,V9*(1+Forecast!$B28))</f>
-        <v>112794212293723.3</v>
+        <v>16557711321225.027</v>
       </c>
       <c r="X9" s="2">
         <f>MAX(0,W9*(1+Forecast!$B28))</f>
-        <v>117869951846940.84</v>
+        <v>17302808330680.152</v>
       </c>
       <c r="Y9" s="2">
         <f>MAX(0,X9*(1+Forecast!$B28))</f>
-        <v>123174099680053.17</v>
+        <v>18081434705560.758</v>
       </c>
       <c r="Z9" s="2">
         <f>MAX(0,Y9*(1+Forecast!$B28))</f>
-        <v>128716934165655.56</v>
+        <v>18895099267310.992</v>
       </c>
       <c r="AA9" s="2">
         <f>MAX(0,Z9*(1+Forecast!$B28))</f>
-        <v>134509196203110.05</v>
+        <v>19745378734339.984</v>
       </c>
       <c r="AB9" s="2">
         <f>MAX(0,AA9*(1+Forecast!$B28))</f>
-        <v>140562110032249.98</v>
+        <v>20633920777385.281</v>
       </c>
       <c r="AC9" s="2">
         <f>MAX(0,AB9*(1+Forecast!$B28))</f>
-        <v>146887404983701.22</v>
+        <v>21562447212367.617</v>
       </c>
       <c r="AD9" s="2">
         <f>MAX(0,AC9*(1+Forecast!$B28))</f>
-        <v>153497338207967.75</v>
+        <v>22532757336924.16</v>
       </c>
       <c r="AE9" s="2">
         <f>MAX(0,AD9*(1+Forecast!$B28))</f>
-        <v>160404718427326.28</v>
+        <v>23546731417085.746</v>
       </c>
       <c r="AF9" s="2">
         <f>MAX(0,AE9*(1+Forecast!$B28))</f>
-        <v>167622930756555.94</v>
+        <v>24606334330854.602</v>
       </c>
       <c r="AG9" s="2">
         <f>MAX(0,AF9*(1+Forecast!$B28))</f>
-        <v>175165962640600.94</v>
+        <v>25713619375743.059</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -43215,7 +45655,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -44646,7 +47086,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>2019</v>
@@ -46077,7 +48517,7 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1">
         <v>2019</v>
@@ -47508,7 +49948,7 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="1">
         <v>2019</v>
@@ -48939,7 +51379,7 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1">
         <v>2019</v>
@@ -50385,12 +52825,12 @@
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1">
         <v>2019</v>
@@ -51821,7 +54261,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -53252,7 +55692,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>2019</v>
@@ -54683,7 +57123,7 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1">
         <v>2019</v>
@@ -56114,7 +58554,7 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="1">
         <v>2019</v>
@@ -57545,7 +59985,7 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1">
         <v>2019</v>
@@ -58978,175 +61418,4 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
-    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44067CE8-66FC-4A82-9FEE-D70C99A00400}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6140F724-F8FB-439D-89B3-32751B1C3108}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA998932-B428-4066-9723-C265089B8E0B}"/>
 </file>
--- a/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
+++ b/InputData/bldgs/BCEU/BAU Components Energy Use.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation-my.sharepoint.com/personal/maryfrancis_energyinnovation_org/Documents/South Korea/4.0.5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\2026\01.EPS\05.EPS고도화\01.EPS 4.0.5 update\v4.0.5\bldgs\BCEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{F24B4FED-E837-4B0B-9935-5BCA717F6EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E83629-6ECF-4A8E-9716-0EC0212E6AA2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C73B541-8CEB-401A-A82A-54318FD4CA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-4770" windowWidth="38640" windowHeight="21120" tabRatio="708" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -523,7 +523,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -539,7 +539,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -556,7 +556,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -567,7 +567,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -583,7 +583,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -594,7 +594,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -746,28 +746,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.000E+00"/>
-    <numFmt numFmtId="168" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="169" formatCode="0.0.E+00"/>
-    <numFmt numFmtId="170" formatCode="0.0_);[Red]\(0.0\)"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.000E+00"/>
+    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="180" formatCode="0.0.E+00"/>
+    <numFmt numFmtId="181" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="182" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -776,14 +776,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -791,7 +791,7 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -799,7 +799,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -807,7 +807,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -834,13 +834,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -849,7 +849,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -857,7 +857,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -865,14 +865,14 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -880,7 +880,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF202124"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -888,7 +888,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF4D5156"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -896,7 +896,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -905,7 +905,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -913,13 +913,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -928,7 +928,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -936,7 +936,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -945,7 +945,7 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF404040"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1208,27 +1208,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="17" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="1"/>
@@ -1257,8 +1257,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="18" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1279,7 +1279,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="18" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1292,15 +1292,15 @@
     <xf numFmtId="11" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="18" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="19" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="19" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="18" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="20" applyBorder="1">
@@ -1312,7 +1312,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="20" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1325,35 +1325,35 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="20" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="7" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="182" fontId="0" fillId="7" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="8" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="182" fontId="0" fillId="8" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="10" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="182" fontId="0" fillId="10" borderId="11" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="20" applyNumberFormat="1">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="20" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="11" xfId="20" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1366,17 +1366,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="24" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="24" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="23">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Body: normal cell 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Comma" xfId="17" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Font: Calibri, 9pt regular 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Footnotes: top row" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
@@ -1384,18 +1389,20 @@
     <cellStyle name="Header: bottom row" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Header: bottom row 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Header: top rows" xfId="16" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="Parent row 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
     <cellStyle name="Table title" xfId="3" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="Table title 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="백분율" xfId="15" builtinId="5"/>
+    <cellStyle name="쉼표" xfId="17" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="19" builtinId="6"/>
     <cellStyle name="쉼표 [0] 2" xfId="22" xr:uid="{945314C0-82D9-466E-B093-13D02BF680DD}"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="18" xr:uid="{C87D6EE6-BA00-4F5B-B77D-E27DCD49F655}"/>
     <cellStyle name="표준 2 2" xfId="21" xr:uid="{548C0212-E988-4B17-8292-DD908D47307B}"/>
     <cellStyle name="표준 3" xfId="20" xr:uid="{BE71BABE-C511-4A7A-9028-0E75FDCCE552}"/>
+    <cellStyle name="하이퍼링크" xfId="7" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1862,19 +1869,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" customWidth="1"/>
-    <col min="2" max="2" width="61.36328125" customWidth="1"/>
-    <col min="3" max="3" width="19.26953125" customWidth="1"/>
+    <col min="1" max="1" width="23.75" customWidth="1"/>
+    <col min="2" max="2" width="61.375" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
@@ -1883,171 +1890,171 @@
       </c>
       <c r="C3" s="10"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="10">
         <v>2020</v>
       </c>
       <c r="C5" s="10"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="10"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="32" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="10"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="10"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="10"/>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="33">
         <v>2023</v>
       </c>
       <c r="C12" s="10"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="33" t="s">
         <v>121</v>
       </c>
       <c r="C13" s="10"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="34" t="s">
         <v>122</v>
       </c>
       <c r="C14" s="10"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>143</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>53</v>
       </c>
@@ -2056,7 +2063,7 @@
       </c>
       <c r="C30" s="10"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>29</v>
       </c>
@@ -2065,7 +2072,7 @@
       </c>
       <c r="C31" s="10"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>30</v>
       </c>
@@ -2074,7 +2081,7 @@
       </c>
       <c r="C32" s="10"/>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>31</v>
       </c>
@@ -2083,7 +2090,7 @@
       </c>
       <c r="C33" s="10"/>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>32</v>
       </c>
@@ -2092,7 +2099,7 @@
       </c>
       <c r="C34" s="10"/>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>33</v>
       </c>
@@ -2101,7 +2108,7 @@
       </c>
       <c r="C35" s="10"/>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>34</v>
       </c>
@@ -2110,7 +2117,7 @@
       </c>
       <c r="C36" s="10"/>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>35</v>
       </c>
@@ -2121,12 +2128,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="e">
         <f>#REF!/(#REF!+#REF!)</f>
         <v>#REF!</v>
@@ -2135,7 +2142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="e">
         <f>#REF!/(#REF!+#REF!)</f>
         <v>#REF!</v>
@@ -2144,7 +2151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2167,18 +2174,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC8465F-F9D9-40CE-B3F9-4DB0BC05364C}">
   <dimension ref="A2:AI73"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="35" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="35" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>37</v>
       </c>
@@ -2281,7 +2288,7 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -2416,7 +2423,7 @@
       <c r="AH4" s="2"/>
       <c r="AI4" s="2"/>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
@@ -2551,7 +2558,7 @@
       <c r="AH5" s="2"/>
       <c r="AI5" s="2"/>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
@@ -2686,7 +2693,7 @@
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
@@ -2821,7 +2828,7 @@
       <c r="AH7" s="2"/>
       <c r="AI7" s="2"/>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>7</v>
       </c>
@@ -2956,7 +2963,7 @@
       <c r="AH8" s="2"/>
       <c r="AI8" s="2"/>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
@@ -3091,7 +3098,7 @@
       <c r="AH9" s="2"/>
       <c r="AI9" s="2"/>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>13</v>
       </c>
@@ -3226,7 +3233,7 @@
       <c r="AH10" s="2"/>
       <c r="AI10" s="2"/>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>14</v>
       </c>
@@ -3361,7 +3368,7 @@
       <c r="AH11" s="2"/>
       <c r="AI11" s="2"/>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
@@ -3496,7 +3503,7 @@
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>16</v>
       </c>
@@ -3631,7 +3638,7 @@
       <c r="AH13" s="2"/>
       <c r="AI13" s="2"/>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>38</v>
       </c>
@@ -3734,7 +3741,7 @@
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>2</v>
       </c>
@@ -3869,7 +3876,7 @@
       <c r="AH16" s="2"/>
       <c r="AI16" s="2"/>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>3</v>
       </c>
@@ -4004,7 +4011,7 @@
       <c r="AH17" s="2"/>
       <c r="AI17" s="2"/>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>4</v>
       </c>
@@ -4139,7 +4146,7 @@
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>5</v>
       </c>
@@ -4274,7 +4281,7 @@
       <c r="AH19" s="2"/>
       <c r="AI19" s="2"/>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>7</v>
       </c>
@@ -4409,7 +4416,7 @@
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>11</v>
       </c>
@@ -4544,7 +4551,7 @@
       <c r="AH21" s="2"/>
       <c r="AI21" s="2"/>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>13</v>
       </c>
@@ -4679,7 +4686,7 @@
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>14</v>
       </c>
@@ -4814,7 +4821,7 @@
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>15</v>
       </c>
@@ -4949,7 +4956,7 @@
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>16</v>
       </c>
@@ -5084,7 +5091,7 @@
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>39</v>
       </c>
@@ -5187,7 +5194,7 @@
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>2</v>
       </c>
@@ -5322,7 +5329,7 @@
       <c r="AH28" s="2"/>
       <c r="AI28" s="2"/>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>3</v>
       </c>
@@ -5457,7 +5464,7 @@
       <c r="AH29" s="2"/>
       <c r="AI29" s="2"/>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>4</v>
       </c>
@@ -5592,7 +5599,7 @@
       <c r="AH30" s="2"/>
       <c r="AI30" s="2"/>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>5</v>
       </c>
@@ -5727,7 +5734,7 @@
       <c r="AH31" s="2"/>
       <c r="AI31" s="2"/>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>7</v>
       </c>
@@ -5862,7 +5869,7 @@
       <c r="AH32" s="2"/>
       <c r="AI32" s="2"/>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>11</v>
       </c>
@@ -5997,7 +6004,7 @@
       <c r="AH33" s="2"/>
       <c r="AI33" s="2"/>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>13</v>
       </c>
@@ -6132,7 +6139,7 @@
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>14</v>
       </c>
@@ -6267,7 +6274,7 @@
       <c r="AH35" s="2"/>
       <c r="AI35" s="2"/>
     </row>
-    <row r="36" spans="1:35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>15</v>
       </c>
@@ -6402,7 +6409,7 @@
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
     </row>
-    <row r="37" spans="1:35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>16</v>
       </c>
@@ -6537,7 +6544,7 @@
       <c r="AH37" s="2"/>
       <c r="AI37" s="2"/>
     </row>
-    <row r="39" spans="1:35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
@@ -6640,7 +6647,7 @@
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>2</v>
       </c>
@@ -6775,7 +6782,7 @@
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>3</v>
       </c>
@@ -6910,7 +6917,7 @@
       <c r="AH41" s="2"/>
       <c r="AI41" s="2"/>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>4</v>
       </c>
@@ -7045,7 +7052,7 @@
       <c r="AH42" s="2"/>
       <c r="AI42" s="2"/>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>5</v>
       </c>
@@ -7180,7 +7187,7 @@
       <c r="AH43" s="2"/>
       <c r="AI43" s="2"/>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>7</v>
       </c>
@@ -7315,7 +7322,7 @@
       <c r="AH44" s="2"/>
       <c r="AI44" s="2"/>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>11</v>
       </c>
@@ -7450,7 +7457,7 @@
       <c r="AH45" s="2"/>
       <c r="AI45" s="2"/>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
         <v>13</v>
       </c>
@@ -7585,7 +7592,7 @@
       <c r="AH46" s="2"/>
       <c r="AI46" s="2"/>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" s="16" t="s">
         <v>14</v>
       </c>
@@ -7720,7 +7727,7 @@
       <c r="AH47" s="2"/>
       <c r="AI47" s="2"/>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
         <v>15</v>
       </c>
@@ -7855,7 +7862,7 @@
       <c r="AH48" s="2"/>
       <c r="AI48" s="2"/>
     </row>
-    <row r="49" spans="1:35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
         <v>16</v>
       </c>
@@ -7990,7 +7997,7 @@
       <c r="AH49" s="2"/>
       <c r="AI49" s="2"/>
     </row>
-    <row r="51" spans="1:35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
         <v>46</v>
       </c>
@@ -8093,7 +8100,7 @@
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
     </row>
-    <row r="52" spans="1:35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
         <v>2</v>
       </c>
@@ -8228,7 +8235,7 @@
       <c r="AH52" s="2"/>
       <c r="AI52" s="2"/>
     </row>
-    <row r="53" spans="1:35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="16" t="s">
         <v>3</v>
       </c>
@@ -8363,7 +8370,7 @@
       <c r="AH53" s="2"/>
       <c r="AI53" s="2"/>
     </row>
-    <row r="54" spans="1:35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>4</v>
       </c>
@@ -8498,7 +8505,7 @@
       <c r="AH54" s="2"/>
       <c r="AI54" s="2"/>
     </row>
-    <row r="55" spans="1:35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>5</v>
       </c>
@@ -8633,7 +8640,7 @@
       <c r="AH55" s="2"/>
       <c r="AI55" s="2"/>
     </row>
-    <row r="56" spans="1:35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
         <v>7</v>
       </c>
@@ -8768,7 +8775,7 @@
       <c r="AH56" s="2"/>
       <c r="AI56" s="2"/>
     </row>
-    <row r="57" spans="1:35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
         <v>11</v>
       </c>
@@ -8903,7 +8910,7 @@
       <c r="AH57" s="2"/>
       <c r="AI57" s="2"/>
     </row>
-    <row r="58" spans="1:35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
         <v>13</v>
       </c>
@@ -9038,7 +9045,7 @@
       <c r="AH58" s="2"/>
       <c r="AI58" s="2"/>
     </row>
-    <row r="59" spans="1:35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
         <v>14</v>
       </c>
@@ -9173,7 +9180,7 @@
       <c r="AH59" s="2"/>
       <c r="AI59" s="2"/>
     </row>
-    <row r="60" spans="1:35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
         <v>15</v>
       </c>
@@ -9308,7 +9315,7 @@
       <c r="AH60" s="2"/>
       <c r="AI60" s="2"/>
     </row>
-    <row r="61" spans="1:35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
         <v>16</v>
       </c>
@@ -9443,7 +9450,7 @@
       <c r="AH61" s="2"/>
       <c r="AI61" s="2"/>
     </row>
-    <row r="63" spans="1:35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
         <v>42</v>
       </c>
@@ -9546,7 +9553,7 @@
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
     </row>
-    <row r="64" spans="1:35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="16" t="s">
         <v>2</v>
       </c>
@@ -9681,7 +9688,7 @@
       <c r="AH64" s="2"/>
       <c r="AI64" s="2"/>
     </row>
-    <row r="65" spans="1:35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
         <v>3</v>
       </c>
@@ -9816,7 +9823,7 @@
       <c r="AH65" s="2"/>
       <c r="AI65" s="2"/>
     </row>
-    <row r="66" spans="1:35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
         <v>4</v>
       </c>
@@ -9951,7 +9958,7 @@
       <c r="AH66" s="2"/>
       <c r="AI66" s="2"/>
     </row>
-    <row r="67" spans="1:35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
         <v>5</v>
       </c>
@@ -10086,7 +10093,7 @@
       <c r="AH67" s="2"/>
       <c r="AI67" s="2"/>
     </row>
-    <row r="68" spans="1:35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="16" t="s">
         <v>7</v>
       </c>
@@ -10221,7 +10228,7 @@
       <c r="AH68" s="2"/>
       <c r="AI68" s="2"/>
     </row>
-    <row r="69" spans="1:35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="16" t="s">
         <v>11</v>
       </c>
@@ -10356,7 +10363,7 @@
       <c r="AH69" s="2"/>
       <c r="AI69" s="2"/>
     </row>
-    <row r="70" spans="1:35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="16" t="s">
         <v>13</v>
       </c>
@@ -10491,7 +10498,7 @@
       <c r="AH70" s="2"/>
       <c r="AI70" s="2"/>
     </row>
-    <row r="71" spans="1:35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>14</v>
       </c>
@@ -10626,7 +10633,7 @@
       <c r="AH71" s="2"/>
       <c r="AI71" s="2"/>
     </row>
-    <row r="72" spans="1:35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
         <v>15</v>
       </c>
@@ -10761,7 +10768,7 @@
       <c r="AH72" s="2"/>
       <c r="AI72" s="2"/>
     </row>
-    <row r="73" spans="1:35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="16" t="s">
         <v>16</v>
       </c>
@@ -10905,22 +10912,22 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF448C0-88C1-4222-975C-12A3F8DE86EE}">
   <dimension ref="A1:AL61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="10" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>54</v>
       </c>
@@ -11036,7 +11043,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>80</v>
       </c>
@@ -11154,7 +11161,7 @@
         <v>3180.5515313473202</v>
       </c>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>82</v>
       </c>
@@ -11272,7 +11279,7 @@
         <v>1885.5083481555948</v>
       </c>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>84</v>
       </c>
@@ -11390,7 +11397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>82</v>
       </c>
@@ -11506,7 +11513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>85</v>
       </c>
@@ -11624,7 +11631,7 @@
         <v>498.09693877551024</v>
       </c>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>82</v>
       </c>
@@ -11742,7 +11749,7 @@
         <v>239.0333333333333</v>
       </c>
     </row>
-    <row r="10" spans="1:38">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>86</v>
       </c>
@@ -11860,7 +11867,7 @@
         <v>1594.612284069098</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>82</v>
       </c>
@@ -11978,7 +11985,7 @@
         <v>457.52849740932641</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>87</v>
       </c>
@@ -12096,7 +12103,7 @@
         <v>561.75103734439836</v>
       </c>
     </row>
-    <row r="13" spans="1:38">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
         <v>82</v>
       </c>
@@ -12214,7 +12221,7 @@
         <v>1111.6965174129352</v>
       </c>
     </row>
-    <row r="14" spans="1:38">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>88</v>
       </c>
@@ -12332,7 +12339,7 @@
         <v>434.6564885496183</v>
       </c>
     </row>
-    <row r="15" spans="1:38">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
         <v>82</v>
       </c>
@@ -12450,7 +12457,7 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="16" spans="1:38">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>89</v>
       </c>
@@ -12568,7 +12575,7 @@
         <v>55.434782608695656</v>
       </c>
     </row>
-    <row r="17" spans="1:38">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>82</v>
       </c>
@@ -12686,7 +12693,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="19" spans="1:38">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>54</v>
       </c>
@@ -12724,7 +12731,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:38">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>80</v>
       </c>
@@ -12762,7 +12769,7 @@
         <v>940666286973619.63</v>
       </c>
     </row>
-    <row r="21" spans="1:38">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>82</v>
       </c>
@@ -12800,7 +12807,7 @@
         <v>903208909273871.63</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>84</v>
       </c>
@@ -12838,7 +12845,7 @@
         <v>7857253800000</v>
       </c>
     </row>
-    <row r="23" spans="1:38">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
         <v>82</v>
       </c>
@@ -12876,7 +12883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>85</v>
       </c>
@@ -12914,7 +12921,7 @@
         <v>113960549819387.77</v>
       </c>
     </row>
-    <row r="25" spans="1:38">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
         <v>82</v>
       </c>
@@ -12952,7 +12959,7 @@
         <v>111977041775862.08</v>
       </c>
     </row>
-    <row r="26" spans="1:38">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>86</v>
       </c>
@@ -12990,7 +12997,7 @@
         <v>430501462928982.81</v>
       </c>
     </row>
-    <row r="27" spans="1:38">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
         <v>82</v>
       </c>
@@ -13028,7 +13035,7 @@
         <v>144142246900000.03</v>
       </c>
     </row>
-    <row r="28" spans="1:38">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>87</v>
       </c>
@@ -13066,7 +13073,7 @@
         <v>266264709351037.41</v>
       </c>
     </row>
-    <row r="29" spans="1:38">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
         <v>82</v>
       </c>
@@ -13104,7 +13111,7 @@
         <v>570221001273267.38</v>
       </c>
     </row>
-    <row r="30" spans="1:38">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>88</v>
       </c>
@@ -13142,7 +13149,7 @@
         <v>95429070691603.063</v>
       </c>
     </row>
-    <row r="31" spans="1:38">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
         <v>82</v>
       </c>
@@ -13180,7 +13187,7 @@
         <v>16349437200000.002</v>
       </c>
     </row>
-    <row r="32" spans="1:38">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>89</v>
       </c>
@@ -13218,7 +13225,7 @@
         <v>26613557282608.699</v>
       </c>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
         <v>82</v>
       </c>
@@ -13256,7 +13263,7 @@
         <v>60876330024742.273</v>
       </c>
     </row>
-    <row r="34" spans="1:37">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" s="38"/>
       <c r="B34" s="38"/>
       <c r="C34" s="18"/>
@@ -13268,7 +13275,7 @@
       <c r="J34" s="31"/>
       <c r="K34" s="31"/>
     </row>
-    <row r="35" spans="1:37">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -13282,12 +13289,12 @@
       <c r="J35" s="31"/>
       <c r="K35" s="31"/>
     </row>
-    <row r="36" spans="1:37">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="37" spans="1:37">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>54</v>
       </c>
@@ -13400,7 +13407,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:37">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>80</v>
       </c>
@@ -13515,7 +13522,7 @@
         <v>542.28104075960391</v>
       </c>
     </row>
-    <row r="39" spans="1:37">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>85</v>
       </c>
@@ -13630,7 +13637,7 @@
         <v>112.52873563218391</v>
       </c>
     </row>
-    <row r="40" spans="1:37">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>86</v>
       </c>
@@ -13745,7 +13752,7 @@
         <v>14.666666666666668</v>
       </c>
     </row>
-    <row r="41" spans="1:37">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>87</v>
       </c>
@@ -13860,7 +13867,7 @@
         <v>268.67326732673268</v>
       </c>
     </row>
-    <row r="42" spans="1:37">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>88</v>
       </c>
@@ -13975,7 +13982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:37">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>89</v>
       </c>
@@ -14090,7 +14097,7 @@
         <v>134.41237113402062</v>
       </c>
     </row>
-    <row r="45" spans="1:37">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
         <v>54</v>
       </c>
@@ -14122,7 +14129,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:37">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>80</v>
       </c>
@@ -14154,7 +14161,7 @@
         <v>218357969473871.66</v>
       </c>
     </row>
-    <row r="47" spans="1:37">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>85</v>
       </c>
@@ -14186,7 +14193,7 @@
         <v>43880842175862.078</v>
       </c>
     </row>
-    <row r="48" spans="1:37">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>86</v>
       </c>
@@ -14218,7 +14225,7 @@
         <v>3584706700000.0005</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>87</v>
       </c>
@@ -14250,7 +14257,7 @@
         <v>112793907573267.33</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>88</v>
       </c>
@@ -14282,7 +14289,7 @@
         <v>2777817000000</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
         <v>89</v>
       </c>
@@ -14314,12 +14321,12 @@
         <v>55360379124742.273</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="40" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -14333,7 +14340,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>80</v>
       </c>
@@ -14350,7 +14357,7 @@
         <v>28263.086269665</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -14367,7 +14374,7 @@
         <v>3927.5632183908046</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -14384,7 +14391,7 @@
         <v>3640.3333333333335</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -14401,7 +14408,7 @@
         <v>17211.732673267325</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -14418,7 +14425,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -14445,18 +14452,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{369EACEB-8E8C-4A24-B652-74E6055FDD6D}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -14485,7 +14492,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -14522,7 +14529,7 @@
         <v>17.533947072930918</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -14559,7 +14566,7 @@
         <v>3.2194777362431484E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -14596,7 +14603,7 @@
         <v>5.6428580995491</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -14633,7 +14640,7 @@
         <v>2.0435788885985261E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -14670,7 +14677,7 @@
         <v>0.56442708031245636</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
@@ -14707,7 +14714,7 @@
         <v>2.4014998105429783</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
@@ -14744,7 +14751,7 @@
         <v>0.14779385458477393</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
@@ -14781,7 +14788,7 @@
         <v>1.6124611879751123E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
@@ -14818,7 +14825,7 @@
         <v>0.31914962808424469</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -14855,7 +14862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="I12" s="2">
         <f>SUM(I2:I11)</f>
@@ -14866,11 +14873,11 @@
         <v>26.646557894543829</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>44</v>
       </c>
@@ -14899,7 +14906,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>2</v>
       </c>
@@ -14936,7 +14943,7 @@
         <v>6.86009529773417</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>3</v>
       </c>
@@ -14973,7 +14980,7 @@
         <v>1.3726727850397179E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>4</v>
       </c>
@@ -15010,7 +15017,7 @@
         <v>8.75040713893633</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>5</v>
       </c>
@@ -15047,7 +15054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>7</v>
       </c>
@@ -15084,7 +15091,7 @@
         <v>2.0402975612109002</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>11</v>
       </c>
@@ -15121,7 +15128,7 @@
         <v>0.13072235567346524</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>13</v>
       </c>
@@ -15158,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>14</v>
       </c>
@@ -15195,7 +15202,7 @@
         <v>0.62141340205954698</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>15</v>
       </c>
@@ -15232,7 +15239,7 @@
         <v>0.23015604320055552</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>16</v>
       </c>
@@ -15269,7 +15276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I25" s="2">
         <f>SUM(I15:I24)</f>
         <v>739963564275514.5</v>
@@ -15279,10 +15286,10 @@
         <v>18.646818526665367</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -15311,7 +15318,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>2</v>
       </c>
@@ -15348,7 +15355,7 @@
         <v>0.61277539696536121</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
@@ -15385,7 +15392,7 @@
         <v>1.2261347317348236E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -15422,7 +15429,7 @@
         <v>0.78162678147361497</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -15459,7 +15466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -15496,7 +15503,7 @@
         <v>0.18224880176393654</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -15533,7 +15540,7 @@
         <v>1.1676724580854189E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -15570,7 +15577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>14</v>
       </c>
@@ -15607,7 +15614,7 @@
         <v>5.550751521664795E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>15</v>
       </c>
@@ -15644,7 +15651,7 @@
         <v>2.0558600808764215E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>16</v>
       </c>
@@ -15681,7 +15688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I38" s="2">
         <f>SUM(I28:I37)</f>
         <v>66096963257725.648</v>
@@ -15691,7 +15698,7 @@
         <v>1.6656199555409141</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <f t="shared" ref="B39:G39" si="3">SUM(B28:B37,B15:B24)</f>
         <v>528631917213651.69</v>
@@ -15717,7 +15724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B40" s="18">
         <f>B39/10^6/About!$B$30/10^6</f>
         <v>13.321336216516645</v>
@@ -15743,7 +15750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -15761,13 +15768,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
     <col min="2" max="32" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -15867,7 +15874,7 @@
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -15997,7 +16004,7 @@
       </c>
       <c r="AH2" s="5"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -16126,7 +16133,7 @@
         <v>162097198270.8522</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -16255,7 +16262,7 @@
         <v>267014182674568.75</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -16384,7 +16391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -16513,7 +16520,7 @@
         <v>80239552122987.672</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -16642,7 +16649,7 @@
         <v>5474409533850.4053</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -16771,7 +16778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -16900,7 +16907,7 @@
         <v>16760068472752.766</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -17029,7 +17036,7 @@
         <v>5131129605466.2002</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -17158,70 +17165,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -17241,13 +17248,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="11.90625" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -17350,7 +17357,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -17483,7 +17490,7 @@
         <v>47698009926925.695</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -17616,7 +17623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -17749,7 +17756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -17882,7 +17889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -18015,7 +18022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -18148,7 +18155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -18281,7 +18288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -18414,7 +18421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -18547,7 +18554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -18693,14 +18700,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -18803,7 +18810,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -18936,7 +18943,7 @@
         <v>47698009926925.695</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -19069,7 +19076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -19202,7 +19209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -19335,7 +19342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -19468,7 +19475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -19601,7 +19608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -19734,7 +19741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -19867,7 +19874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -20000,7 +20007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -20146,13 +20153,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="13.6328125" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -20255,7 +20262,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -20388,7 +20395,7 @@
         <v>109378314244044.11</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -20521,7 +20528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -20654,7 +20661,7 @@
         <v>55564771659181.594</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -20787,7 +20794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -20920,7 +20927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -21053,7 +21060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -21186,7 +21193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -21319,7 +21326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -21452,7 +21459,7 @@
         <v>1031174169336.6079</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -21598,13 +21605,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="13.08984375" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -21707,7 +21714,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -21840,7 +21847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -21973,7 +21980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -22106,7 +22113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -22239,7 +22246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -22372,7 +22379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -22505,7 +22512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -22638,7 +22645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -22771,7 +22778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -22904,7 +22911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -23050,13 +23057,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="10.26953125" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -23159,7 +23166,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -23292,7 +23299,7 @@
         <v>7524477894781.333</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -23425,7 +23432,7 @@
         <v>12654882359.12356</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -23558,7 +23565,7 @@
         <v>23660132544095.98</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -23691,7 +23698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -23824,7 +23831,7 @@
         <v>7160200033563.0723</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -23957,7 +23964,7 @@
         <v>491933541684.51801</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -24090,7 +24097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -24223,7 +24230,7 @@
         <v>1434209083818.6985</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -24356,7 +24363,7 @@
         <v>439086075476.03766</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -24502,13 +24509,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="12.26953125" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -24611,7 +24618,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -24744,7 +24751,7 @@
         <v>4260606551206.8677</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -24877,7 +24884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -25010,7 +25017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -25143,7 +25150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -25276,7 +25283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -25409,7 +25416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -25542,7 +25549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -25675,7 +25682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -25808,7 +25815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -25951,16 +25958,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED6D3F1-92E7-40E9-A07E-C7DBA9C24A0B}">
   <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -26004,7 +26011,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -26048,7 +26055,7 @@
         <v>69300936097001.828</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -26092,7 +26099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -26136,7 +26143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -26180,7 +26187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -26224,7 +26231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
@@ -26268,7 +26275,7 @@
         <v>3793426578300.001</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
@@ -26312,7 +26319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
@@ -26356,7 +26363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
@@ -26400,7 +26407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -26444,10 +26451,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>44</v>
       </c>
@@ -26491,7 +26498,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -26537,7 +26544,7 @@
       </c>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -26577,7 +26584,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>4</v>
       </c>
@@ -26619,7 +26626,7 @@
       </c>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>5</v>
       </c>
@@ -26657,7 +26664,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>7</v>
       </c>
@@ -26697,7 +26704,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>11</v>
       </c>
@@ -26737,7 +26744,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>13</v>
       </c>
@@ -26775,7 +26782,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>14</v>
       </c>
@@ -26815,7 +26822,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>15</v>
       </c>
@@ -26857,7 +26864,7 @@
       </c>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>16</v>
       </c>
@@ -26895,7 +26902,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
@@ -26918,7 +26925,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
@@ -26947,7 +26954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -26976,7 +26983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -27005,7 +27012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -27034,7 +27041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -27063,7 +27070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -27092,7 +27099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -27121,7 +27128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
@@ -27150,7 +27157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -27179,7 +27186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -27220,14 +27227,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -27330,7 +27337,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -27463,7 +27470,7 @@
         <v>4260606551206.8677</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -27596,7 +27603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -27729,7 +27736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -27862,7 +27869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -27995,7 +28002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -28128,7 +28135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -28261,7 +28268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -28394,7 +28401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -28527,7 +28534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -28673,16 +28680,16 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="9.6328125" customWidth="1"/>
-    <col min="3" max="31" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="31" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -28785,7 +28792,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -28918,7 +28925,7 @@
         <v>9770176217877.5801</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -29051,7 +29058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -29184,7 +29191,7 @@
         <v>4963302043630.5957</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -29317,7 +29324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -29450,7 +29457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -29583,7 +29590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -29716,7 +29723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -29849,7 +29856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -29982,7 +29989,7 @@
         <v>92109239526.799377</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -30128,14 +30135,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -30238,7 +30245,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -30371,7 +30378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -30504,7 +30511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -30637,7 +30644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -30770,7 +30777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -30903,7 +30910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -31036,7 +31043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -31169,7 +31176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -31302,7 +31309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -31435,7 +31442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -31581,17 +31588,17 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="32" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.90625" customWidth="1"/>
+    <col min="6" max="32" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -31694,7 +31701,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -31827,7 +31834,7 @@
         <v>172393688974070.81</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -31960,7 +31967,7 @@
         <v>2348870064.8602166</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -32093,7 +32100,7 @@
         <v>105721419066266.25</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -32226,7 +32233,7 @@
         <v>126888121609.30501</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -32359,7 +32366,7 @@
         <v>24766062481213.523</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -32492,7 +32499,7 @@
         <v>52626726653019.188</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -32625,7 +32632,7 @@
         <v>3260979454194.9014</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -32758,7 +32765,7 @@
         <v>386622524795.51202</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -32891,7 +32898,7 @@
         <v>2784341068955.522</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -33037,14 +33044,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -33147,25 +33154,25 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="63">
         <f>Commercial_calculation!B16-'Scenarios_from BDEU'!B33</f>
-        <v>186341505350015.66</v>
+        <v>186341505351074.06</v>
       </c>
       <c r="C2" s="63">
         <f>Commercial_calculation!C16-'Scenarios_from BDEU'!C33</f>
-        <v>189203681919134</v>
+        <v>189203681920192.41</v>
       </c>
       <c r="D2" s="63">
         <f>Commercial_calculation!D16-'Scenarios_from BDEU'!D33</f>
-        <v>190877467832768.69</v>
+        <v>190877467833474.31</v>
       </c>
       <c r="E2" s="63">
         <f>Commercial_calculation!E16-'Scenarios_from BDEU'!E33</f>
-        <v>201799585119994.47</v>
+        <v>201799585120347.28</v>
       </c>
       <c r="F2" s="63">
         <f>Commercial_calculation!F16-'Scenarios_from BDEU'!F33</f>
@@ -33280,7 +33287,7 @@
         <v>252240702965562.84</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -33413,7 +33420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -33546,7 +33553,7 @@
         <v>42585834541561.742</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -33679,7 +33686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -33812,7 +33819,7 @@
         <v>2006578473973.9128</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -33945,7 +33952,7 @@
         <v>17917771355296.383</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -34078,7 +34085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -34211,7 +34218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -34344,7 +34351,7 @@
         <v>371693213892.07074</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -34490,14 +34497,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -34600,7 +34607,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -34733,7 +34740,7 @@
         <v>145017953729354.16</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -34866,7 +34873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -34999,7 +35006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -35132,7 +35139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -35265,7 +35272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -35398,7 +35405,7 @@
         <v>18390598193173.477</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -35531,7 +35538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -35664,7 +35671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -35797,7 +35804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -35943,13 +35950,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="10.08984375" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -36052,7 +36059,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -36185,7 +36192,7 @@
         <v>90051330880520.109</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -36318,7 +36325,7 @@
         <v>2792735925.686161</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -36451,7 +36458,7 @@
         <v>124657415526361.92</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -36584,7 +36591,7 @@
         <v>368980335136.19299</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -36717,7 +36724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -36850,7 +36857,7 @@
         <v>27208602132235.035</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -36983,7 +36990,7 @@
         <v>325195319790.93268</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -37116,7 +37123,7 @@
         <v>4636479348.7177896</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -37249,7 +37256,7 @@
         <v>4588038355207.7549</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -37395,13 +37402,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -37504,25 +37511,25 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="63">
         <f>Commercial_calculation!B64-SUM('Scenarios_from BDEU'!B34:B35)</f>
-        <v>69300936083097.352</v>
+        <v>69300936087760.18</v>
       </c>
       <c r="C2" s="63">
         <f>Commercial_calculation!C64-SUM('Scenarios_from BDEU'!C34:C35)</f>
-        <v>70365392965115.039</v>
+        <v>70365392969777.867</v>
       </c>
       <c r="D2" s="63">
         <f>Commercial_calculation!D64-SUM('Scenarios_from BDEU'!D34:D35)</f>
-        <v>70987881791980.641</v>
+        <v>70987881795089.203</v>
       </c>
       <c r="E2" s="63">
         <f>Commercial_calculation!E64-SUM('Scenarios_from BDEU'!E34:E35)</f>
-        <v>75049868406654.484</v>
+        <v>75049868408208.766</v>
       </c>
       <c r="F2" s="63">
         <f>Commercial_calculation!F64-SUM('Scenarios_from BDEU'!F34:F35)</f>
@@ -37637,7 +37644,7 @@
         <v>93809070708299.172</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -37770,7 +37777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -37903,7 +37910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -38036,7 +38043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -38169,7 +38176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -38302,7 +38309,7 @@
         <v>31852668014930.297</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -38435,7 +38442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -38568,7 +38575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -38701,7 +38708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -38847,13 +38854,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.90625" customWidth="1"/>
-    <col min="2" max="33" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" width="29.875" customWidth="1"/>
+    <col min="2" max="33" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -38956,7 +38963,7 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -39057,7 +39064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -39158,7 +39165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -39259,7 +39266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -39360,7 +39367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -39461,7 +39468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -39562,7 +39569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -39663,7 +39670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -39764,7 +39771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -39865,7 +39872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -39976,12 +39983,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C5634-8E37-4102-BD51-07591524D1A5}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultColWidth="14.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="14.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -40025,7 +40032,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -40075,7 +40082,7 @@
         <v>70365392979019.516</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -40125,7 +40132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -40175,7 +40182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -40225,7 +40232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -40275,7 +40282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
@@ -40325,7 +40332,7 @@
         <v>12213394673416.766</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
@@ -40375,7 +40382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
@@ -40425,7 +40432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
@@ -40475,7 +40482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -40525,10 +40532,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>44</v>
       </c>
@@ -40572,7 +40579,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -40618,7 +40625,7 @@
       </c>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -40658,7 +40665,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>4</v>
       </c>
@@ -40700,7 +40707,7 @@
       </c>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>5</v>
       </c>
@@ -40738,7 +40745,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>7</v>
       </c>
@@ -40778,7 +40785,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>11</v>
       </c>
@@ -40818,7 +40825,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>13</v>
       </c>
@@ -40856,7 +40863,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>14</v>
       </c>
@@ -40896,7 +40903,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>15</v>
       </c>
@@ -40938,7 +40945,7 @@
       </c>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>16</v>
       </c>
@@ -40976,7 +40983,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
@@ -40999,7 +41006,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
@@ -41028,7 +41035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -41057,7 +41064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -41086,7 +41093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -41115,7 +41122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -41144,7 +41151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -41173,7 +41180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -41202,7 +41209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
@@ -41231,7 +41238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -41260,7 +41267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -41298,14 +41305,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B3329B-C745-41ED-9C35-7E1E1BEFFFDB}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultColWidth="11.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.90625" style="16"/>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="16"/>
     <col min="10" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -41334,7 +41341,7 @@
       <c r="N1" s="16"/>
       <c r="O1" s="16"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -41363,7 +41370,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -41392,7 +41399,7 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -41421,7 +41428,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -41450,7 +41457,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -41479,7 +41486,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
@@ -41508,7 +41515,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
@@ -41537,7 +41544,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
@@ -41566,7 +41573,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
@@ -41595,7 +41602,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -41624,10 +41631,10 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>44</v>
       </c>
@@ -41656,7 +41663,7 @@
       <c r="N13" s="16"/>
       <c r="O13" s="16"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
@@ -41685,7 +41692,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
@@ -41714,7 +41721,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>4</v>
       </c>
@@ -41743,7 +41750,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>5</v>
       </c>
@@ -41772,7 +41779,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>7</v>
       </c>
@@ -41801,7 +41808,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>11</v>
       </c>
@@ -41830,7 +41837,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>13</v>
       </c>
@@ -41859,7 +41866,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>14</v>
       </c>
@@ -41888,7 +41895,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>15</v>
       </c>
@@ -41917,7 +41924,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>16</v>
       </c>
@@ -41946,10 +41953,10 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
@@ -41973,7 +41980,7 @@
       </c>
       <c r="I25"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
@@ -41997,7 +42004,7 @@
       </c>
       <c r="I26"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -42020,7 +42027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -42043,7 +42050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -42066,7 +42073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -42089,7 +42096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -42112,7 +42119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -42135,7 +42142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
@@ -42158,7 +42165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -42181,7 +42188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -42213,12 +42220,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886F7208-D733-450A-914C-161D4AB34DE1}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
@@ -42241,7 +42248,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
@@ -42264,7 +42271,7 @@
         <v>75049868420558.969</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -42287,7 +42294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -42310,7 +42317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -42333,7 +42340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -42356,7 +42363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>11</v>
       </c>
@@ -42379,7 +42386,7 @@
         <v>9287304453058.3164</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
@@ -42402,7 +42409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>14</v>
       </c>
@@ -42425,7 +42432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
@@ -42448,7 +42455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -42480,13 +42487,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67CFF0D5-CCA6-41D0-9ADB-4D3C10D15974}">
   <dimension ref="A2:F32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -42494,7 +42501,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
@@ -42502,7 +42509,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
@@ -42510,7 +42517,7 @@
         <v>-0.126</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>4</v>
       </c>
@@ -42518,7 +42525,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>5</v>
       </c>
@@ -42526,7 +42533,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
@@ -42534,7 +42541,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>11</v>
       </c>
@@ -42542,7 +42549,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>13</v>
       </c>
@@ -42550,7 +42557,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>14</v>
       </c>
@@ -42558,7 +42565,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>15</v>
       </c>
@@ -42566,7 +42573,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>16</v>
       </c>
@@ -42574,7 +42581,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>125</v>
       </c>
@@ -42582,7 +42589,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>37</v>
       </c>
@@ -42590,7 +42597,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>38</v>
       </c>
@@ -42598,7 +42605,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>39</v>
       </c>
@@ -42606,7 +42613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>40</v>
       </c>
@@ -42614,7 +42621,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>41</v>
       </c>
@@ -42622,7 +42629,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>42</v>
       </c>
@@ -42630,7 +42637,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -42638,7 +42645,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>2</v>
       </c>
@@ -42646,7 +42653,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>3</v>
       </c>
@@ -42660,7 +42667,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>4</v>
       </c>
@@ -42668,7 +42675,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>5</v>
       </c>
@@ -42676,7 +42683,7 @@
         <v>-4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>7</v>
       </c>
@@ -42684,7 +42691,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>11</v>
       </c>
@@ -42692,7 +42699,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>13</v>
       </c>
@@ -42700,7 +42707,7 @@
         <v>-4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>14</v>
       </c>
@@ -42708,7 +42715,7 @@
         <v>-4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>15</v>
       </c>
@@ -42716,7 +42723,7 @@
         <v>-4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>16</v>
       </c>
@@ -42733,19 +42740,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB321F69-219E-4ABD-864E-501FE2C1AAFB}">
   <dimension ref="A2:AG102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>37</v>
       </c>
@@ -42846,7 +42853,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -42979,7 +42986,7 @@
         <v>172393688974070.81</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
@@ -43112,7 +43119,7 @@
         <v>2348870064.8602166</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
@@ -43245,7 +43252,7 @@
         <v>105721419066266.25</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
@@ -43378,7 +43385,7 @@
         <v>126888121609.30501</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>7</v>
       </c>
@@ -43511,7 +43518,7 @@
         <v>24766062481213.523</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
@@ -43644,7 +43651,7 @@
         <v>52626726653019.188</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>13</v>
       </c>
@@ -43777,7 +43784,7 @@
         <v>3260979454194.9014</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>14</v>
       </c>
@@ -43910,7 +43917,7 @@
         <v>386622524795.51202</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
@@ -44043,7 +44050,7 @@
         <v>2784341068955.522</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>16</v>
       </c>
@@ -44176,7 +44183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>38</v>
       </c>
@@ -44277,7 +44284,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:33" s="62" customFormat="1">
+    <row r="16" spans="1:33" s="62" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="60" t="s">
         <v>2</v>
       </c>
@@ -44410,7 +44417,7 @@
         <v>252240702987863.34</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>3</v>
       </c>
@@ -44543,7 +44550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>4</v>
       </c>
@@ -44676,7 +44683,7 @@
         <v>42585834541561.742</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>5</v>
       </c>
@@ -44809,7 +44816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>7</v>
       </c>
@@ -44942,7 +44949,7 @@
         <v>2006578473973.9128</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>11</v>
       </c>
@@ -45075,7 +45082,7 @@
         <v>17917771355296.383</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>13</v>
       </c>
@@ -45208,7 +45215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>14</v>
       </c>
@@ -45341,7 +45348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>15</v>
       </c>
@@ -45474,7 +45481,7 @@
         <v>371693213892.07074</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>16</v>
       </c>
@@ -45607,7 +45614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B26" s="37"/>
       <c r="C26" s="37"/>
       <c r="D26" s="37"/>
@@ -45641,7 +45648,7 @@
       <c r="AF26" s="37"/>
       <c r="AG26" s="37"/>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>39</v>
       </c>
@@ -45742,7 +45749,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>2</v>
       </c>
@@ -45875,7 +45882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>3</v>
       </c>
@@ -46008,7 +46015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>4</v>
       </c>
@@ -46141,7 +46148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>5</v>
       </c>
@@ -46274,7 +46281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>7</v>
       </c>
@@ -46407,7 +46414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>11</v>
       </c>
@@ -46540,7 +46547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>13</v>
       </c>
@@ -46673,7 +46680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>14</v>
       </c>
@@ -46806,7 +46813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>15</v>
       </c>
@@ -46939,7 +46946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>16</v>
       </c>
@@ -47072,7 +47079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:33">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
@@ -47173,7 +47180,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:33">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>2</v>
       </c>
@@ -47306,7 +47313,7 @@
         <v>145017953729354.16</v>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>3</v>
       </c>
@@ -47439,7 +47446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:33">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>4</v>
       </c>
@@ -47572,7 +47579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:33">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>5</v>
       </c>
@@ -47705,7 +47712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:33">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>7</v>
       </c>
@@ -47838,7 +47845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:33">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>11</v>
       </c>
@@ -47971,7 +47978,7 @@
         <v>18390598193173.477</v>
       </c>
     </row>
-    <row r="46" spans="1:33">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
         <v>13</v>
       </c>
@@ -48104,7 +48111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:33">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="16" t="s">
         <v>14</v>
       </c>
@@ -48237,7 +48244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:33">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
         <v>15</v>
       </c>
@@ -48370,7 +48377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:33">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
         <v>16</v>
       </c>
@@ -48503,7 +48510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:33">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
         <v>46</v>
       </c>
@@ -48604,7 +48611,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="52" spans="1:33">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
         <v>2</v>
       </c>
@@ -48737,7 +48744,7 @@
         <v>90051330880520.109</v>
       </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="16" t="s">
         <v>3</v>
       </c>
@@ -48870,7 +48877,7 @@
         <v>2792735925.686161</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>4</v>
       </c>
@@ -49003,7 +49010,7 @@
         <v>124657415526361.92</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>5</v>
       </c>
@@ -49136,7 +49143,7 @@
         <v>368980335136.19299</v>
       </c>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
         <v>7</v>
       </c>
@@ -49269,7 +49276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
         <v>11</v>
       </c>
@@ -49402,7 +49409,7 @@
         <v>27208602132235.035</v>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
         <v>13</v>
       </c>
@@ -49535,7 +49542,7 @@
         <v>325195319790.93268</v>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
         <v>14</v>
       </c>
@@ -49668,7 +49675,7 @@
         <v>4636479348.7177896</v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
         <v>15</v>
       </c>
@@ -49801,7 +49808,7 @@
         <v>4588038355207.7549</v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
         <v>16</v>
       </c>
@@ -49934,7 +49941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
         <v>42</v>
       </c>
@@ -50035,7 +50042,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="64" spans="1:33" s="62" customFormat="1">
+    <row r="64" spans="1:33" s="62" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="60" t="s">
         <v>2</v>
       </c>
@@ -50168,7 +50175,7 @@
         <v>93809070806541.953</v>
       </c>
     </row>
-    <row r="65" spans="1:33">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
         <v>3</v>
       </c>
@@ -50301,7 +50308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:33">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
         <v>4</v>
       </c>
@@ -50434,7 +50441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
         <v>5</v>
       </c>
@@ -50567,7 +50574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="16" t="s">
         <v>7</v>
       </c>
@@ -50700,7 +50707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:33">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="16" t="s">
         <v>11</v>
       </c>
@@ -50833,7 +50840,7 @@
         <v>31852668014930.297</v>
       </c>
     </row>
-    <row r="70" spans="1:33">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="16" t="s">
         <v>13</v>
       </c>
@@ -50966,7 +50973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>14</v>
       </c>
@@ -51099,7 +51106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:33">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
         <v>15</v>
       </c>
@@ -51232,7 +51239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="16" t="s">
         <v>16</v>
       </c>
@@ -51365,12 +51372,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:33">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:33">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>132</v>
       </c>
@@ -51471,7 +51478,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="78" spans="1:33">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A78" s="16" t="s">
         <v>2</v>
       </c>
@@ -51604,7 +51611,7 @@
         <v>753512747378350.5</v>
       </c>
     </row>
-    <row r="79" spans="1:33">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A79" s="16" t="s">
         <v>3</v>
       </c>
@@ -51737,7 +51744,7 @@
         <v>5141605990.5463772</v>
       </c>
     </row>
-    <row r="80" spans="1:33">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A80" s="16" t="s">
         <v>4</v>
       </c>
@@ -51870,7 +51877,7 @@
         <v>272964669134189.91</v>
       </c>
     </row>
-    <row r="81" spans="1:33">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A81" s="16" t="s">
         <v>5</v>
       </c>
@@ -52003,7 +52010,7 @@
         <v>495868456745.49799</v>
       </c>
     </row>
-    <row r="82" spans="1:33">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82" s="16" t="s">
         <v>7</v>
       </c>
@@ -52136,7 +52143,7 @@
         <v>26772640955187.438</v>
       </c>
     </row>
-    <row r="83" spans="1:33">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A83" s="16" t="s">
         <v>11</v>
       </c>
@@ -52269,7 +52276,7 @@
         <v>147996366348654.38</v>
       </c>
     </row>
-    <row r="84" spans="1:33">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A84" s="16" t="s">
         <v>13</v>
       </c>
@@ -52402,7 +52409,7 @@
         <v>3586174773985.834</v>
       </c>
     </row>
-    <row r="85" spans="1:33">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A85" s="16" t="s">
         <v>14</v>
       </c>
@@ -52535,7 +52542,7 @@
         <v>391259004144.2298</v>
       </c>
     </row>
-    <row r="86" spans="1:33">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A86" s="16" t="s">
         <v>15</v>
       </c>
@@ -52668,7 +52675,7 @@
         <v>7744072638055.3477</v>
       </c>
     </row>
-    <row r="87" spans="1:33">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A87" s="16" t="s">
         <v>16</v>
       </c>
@@ -52801,7 +52808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:33">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>132</v>
       </c>
@@ -52902,7 +52909,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="93" spans="1:33">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A93" s="16" t="s">
         <v>142</v>
       </c>
@@ -53035,7 +53042,7 @@
         <v>220.83276351873707</v>
       </c>
     </row>
-    <row r="94" spans="1:33">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94" s="16" t="s">
         <v>133</v>
       </c>
@@ -53168,7 +53175,7 @@
         <v>1.5068558080368218E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:33">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95" s="16" t="s">
         <v>134</v>
       </c>
@@ -53301,7 +53308,7 @@
         <v>79.998039101007492</v>
       </c>
     </row>
-    <row r="96" spans="1:33">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96" s="16" t="s">
         <v>135</v>
       </c>
@@ -53434,7 +53441,7 @@
         <v>0.14532468365780146</v>
       </c>
     </row>
-    <row r="97" spans="1:33">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97" s="16" t="s">
         <v>136</v>
       </c>
@@ -53567,7 +53574,7 @@
         <v>7.8462856924440532</v>
       </c>
     </row>
-    <row r="98" spans="1:33">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98" s="16" t="s">
         <v>137</v>
       </c>
@@ -53700,7 +53707,7 @@
         <v>43.373448803905106</v>
       </c>
     </row>
-    <row r="99" spans="1:33">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99" s="16" t="s">
         <v>138</v>
       </c>
@@ -53833,7 +53840,7 @@
         <v>1.0510039658331436</v>
       </c>
     </row>
-    <row r="100" spans="1:33">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100" s="16" t="s">
         <v>139</v>
       </c>
@@ -53966,7 +53973,7 @@
         <v>0.11466668273015303</v>
       </c>
     </row>
-    <row r="101" spans="1:33">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101" s="16" t="s">
         <v>140</v>
       </c>
@@ -54099,7 +54106,7 @@
         <v>2.269563411503785</v>
       </c>
     </row>
-    <row r="102" spans="1:33">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102" s="16" t="s">
         <v>141</v>
       </c>
@@ -54241,21 +54248,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BC8619-23DE-4597-BAF2-AFC024F3520B}">
   <dimension ref="A1:AG36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7265625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" style="41" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.75" style="41" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="41" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="9" style="41"/>
-    <col min="8" max="8" width="17.36328125" style="41" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="41" customWidth="1"/>
     <col min="9" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="65" customFormat="1">
+    <row r="1" spans="1:32" s="65" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="64" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
         <v>145</v>
       </c>
@@ -54281,7 +54288,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
         <v>153</v>
       </c>
@@ -54307,7 +54314,7 @@
         <v>7.703296142690097E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="46" t="s">
         <v>154</v>
       </c>
@@ -54333,7 +54340,7 @@
         <v>6.6003581778052212E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="42" t="s">
         <v>145</v>
       </c>
@@ -54354,7 +54361,7 @@
       </c>
       <c r="G5" s="43"/>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" s="46" t="s">
         <v>155</v>
       </c>
@@ -54375,392 +54382,428 @@
       </c>
       <c r="G6" s="43"/>
     </row>
-    <row r="9" spans="1:29" s="65" customFormat="1">
+    <row r="9" spans="1:32" s="65" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="67" customFormat="1">
+    <row r="10" spans="1:32" s="67" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="67" customFormat="1">
+    <row r="11" spans="1:32" s="67" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="66" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="71">
+        <v>2020</v>
+      </c>
+      <c r="C12" s="71">
+        <v>2021</v>
+      </c>
+      <c r="D12" s="71">
+        <v>2022</v>
+      </c>
+      <c r="E12" s="43">
         <v>2023</v>
       </c>
-      <c r="C12" s="43">
+      <c r="F12" s="43">
         <v>2024</v>
       </c>
-      <c r="D12" s="43">
+      <c r="G12" s="43">
         <v>2025</v>
       </c>
-      <c r="E12" s="43">
+      <c r="H12" s="43">
         <v>2026</v>
       </c>
-      <c r="F12" s="43">
+      <c r="I12" s="43">
         <v>2027</v>
       </c>
-      <c r="G12" s="43">
+      <c r="J12" s="43">
         <v>2028</v>
       </c>
-      <c r="H12" s="43">
+      <c r="K12" s="43">
         <v>2029</v>
       </c>
-      <c r="I12" s="43">
+      <c r="L12" s="43">
         <v>2030</v>
       </c>
-      <c r="J12" s="43">
+      <c r="M12" s="43">
         <v>2031</v>
       </c>
-      <c r="K12" s="43">
+      <c r="N12" s="43">
         <v>2032</v>
       </c>
-      <c r="L12" s="43">
+      <c r="O12" s="43">
         <v>2033</v>
       </c>
-      <c r="M12" s="43">
+      <c r="P12" s="43">
         <v>2034</v>
       </c>
-      <c r="N12" s="43">
+      <c r="Q12" s="43">
         <v>2035</v>
       </c>
-      <c r="O12" s="43">
+      <c r="R12" s="43">
         <v>2036</v>
       </c>
-      <c r="P12" s="43">
+      <c r="S12" s="43">
         <v>2037</v>
       </c>
-      <c r="Q12" s="43">
+      <c r="T12" s="43">
         <v>2038</v>
       </c>
-      <c r="R12" s="43">
+      <c r="U12" s="43">
         <v>2039</v>
       </c>
-      <c r="S12" s="43">
+      <c r="V12" s="43">
         <v>2040</v>
       </c>
-      <c r="T12" s="43">
+      <c r="W12" s="43">
         <v>2041</v>
       </c>
-      <c r="U12" s="43">
+      <c r="X12" s="43">
         <v>2042</v>
       </c>
-      <c r="V12" s="43">
+      <c r="Y12" s="43">
         <v>2043</v>
       </c>
-      <c r="W12" s="43">
+      <c r="Z12" s="43">
         <v>2044</v>
       </c>
-      <c r="X12" s="43">
+      <c r="AA12" s="43">
         <v>2045</v>
       </c>
-      <c r="Y12" s="43">
+      <c r="AB12" s="43">
         <v>2046</v>
       </c>
-      <c r="Z12" s="43">
+      <c r="AC12" s="43">
         <v>2047</v>
       </c>
-      <c r="AA12" s="43">
+      <c r="AD12" s="43">
         <v>2048</v>
       </c>
-      <c r="AB12" s="43">
+      <c r="AE12" s="43">
         <v>2049</v>
       </c>
-      <c r="AC12" s="43">
+      <c r="AF12" s="43">
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="72">
+        <v>3.3232628398789075</v>
+      </c>
+      <c r="C13" s="72">
+        <v>3.8821752265860141</v>
+      </c>
+      <c r="D13" s="72">
+        <v>4.4410876132930506</v>
+      </c>
+      <c r="E13" s="51">
         <v>5</v>
       </c>
-      <c r="C13" s="52">
+      <c r="F13" s="52">
         <v>5.25</v>
       </c>
-      <c r="D13" s="51">
+      <c r="G13" s="51">
         <v>5.4999999999999991</v>
       </c>
-      <c r="E13" s="52">
+      <c r="H13" s="52">
         <v>5.9500000000000455</v>
       </c>
-      <c r="F13" s="51">
+      <c r="I13" s="51">
         <v>6.4</v>
       </c>
-      <c r="G13" s="52">
+      <c r="J13" s="52">
         <v>6.933333333333394</v>
       </c>
-      <c r="H13" s="52">
+      <c r="K13" s="52">
         <v>7.466666666666697</v>
       </c>
-      <c r="I13" s="51">
+      <c r="L13" s="51">
         <v>8</v>
       </c>
-      <c r="J13" s="52">
+      <c r="M13" s="52">
         <v>8.75</v>
       </c>
-      <c r="K13" s="52">
+      <c r="N13" s="52">
         <v>9.5</v>
       </c>
-      <c r="L13" s="52">
+      <c r="O13" s="52">
         <v>10.25</v>
       </c>
-      <c r="M13" s="52">
+      <c r="P13" s="52">
         <v>11</v>
       </c>
-      <c r="N13" s="52">
+      <c r="Q13" s="52">
         <v>11.75</v>
       </c>
-      <c r="O13" s="51">
+      <c r="R13" s="51">
         <v>12.499999999999998</v>
       </c>
-      <c r="P13" s="52">
+      <c r="S13" s="52">
         <v>13.5</v>
       </c>
-      <c r="Q13" s="51">
+      <c r="T13" s="51">
         <v>14.5</v>
       </c>
-      <c r="R13" s="52">
+      <c r="U13" s="52">
         <v>15.616977940690065</v>
       </c>
-      <c r="S13" s="52">
+      <c r="V13" s="52">
         <v>16.820000000000007</v>
       </c>
-      <c r="T13" s="52">
+      <c r="W13" s="52">
         <v>18.115694411200483</v>
       </c>
-      <c r="U13" s="52">
+      <c r="X13" s="52">
         <v>19.511200000000017</v>
       </c>
-      <c r="V13" s="52">
+      <c r="Y13" s="52">
         <v>21.014205516992568</v>
       </c>
-      <c r="W13" s="52">
+      <c r="Z13" s="52">
         <v>22.632992000000026</v>
       </c>
-      <c r="X13" s="52">
+      <c r="AA13" s="52">
         <v>24.376478399711388</v>
       </c>
-      <c r="Y13" s="52">
+      <c r="AB13" s="52">
         <v>26.25427072000004</v>
       </c>
-      <c r="Z13" s="52">
+      <c r="AC13" s="52">
         <v>28.276714943665219</v>
       </c>
-      <c r="AA13" s="52">
+      <c r="AD13" s="52">
         <v>30.454954035200057</v>
       </c>
-      <c r="AB13" s="52">
+      <c r="AE13" s="52">
         <v>32.800989334651668</v>
       </c>
-      <c r="AC13" s="52">
+      <c r="AF13" s="52">
         <v>35.327746680832078</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="53">
+      <c r="B14" s="72">
+        <v>3.3232628398789075</v>
+      </c>
+      <c r="C14" s="72">
+        <v>3.8821752265860141</v>
+      </c>
+      <c r="D14" s="72">
+        <v>4.4410876132930506</v>
+      </c>
+      <c r="E14" s="53">
         <v>5</v>
       </c>
-      <c r="C14" s="52">
+      <c r="F14" s="52">
         <v>6.5999999999999091</v>
       </c>
-      <c r="D14" s="53">
+      <c r="G14" s="53">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E14" s="52">
+      <c r="H14" s="52">
         <v>11.5</v>
       </c>
-      <c r="F14" s="53">
+      <c r="I14" s="53">
         <v>14.8</v>
       </c>
-      <c r="G14" s="52">
+      <c r="J14" s="52">
         <v>15.866666666666788</v>
       </c>
-      <c r="H14" s="52">
+      <c r="K14" s="52">
         <v>16.933333333333394</v>
       </c>
-      <c r="I14" s="53">
+      <c r="L14" s="53">
         <v>18</v>
       </c>
-      <c r="J14" s="52">
+      <c r="M14" s="52">
         <v>19.399999999999636</v>
       </c>
-      <c r="K14" s="52">
+      <c r="N14" s="52">
         <v>20.799999999999727</v>
       </c>
-      <c r="L14" s="52">
+      <c r="O14" s="52">
         <v>22.199999999999818</v>
       </c>
-      <c r="M14" s="52">
+      <c r="P14" s="52">
         <v>23.599999999999909</v>
       </c>
-      <c r="N14" s="52">
+      <c r="Q14" s="52">
         <v>25</v>
       </c>
-      <c r="O14" s="53">
+      <c r="R14" s="53">
         <v>26.4</v>
       </c>
-      <c r="P14" s="52">
+      <c r="S14" s="52">
         <v>28.199999999999818</v>
       </c>
-      <c r="Q14" s="53">
+      <c r="T14" s="53">
         <v>30</v>
       </c>
-      <c r="R14" s="52">
+      <c r="U14" s="52">
         <v>31.980107453341567</v>
       </c>
-      <c r="S14" s="52">
+      <c r="V14" s="52">
         <v>34.090909090909093</v>
       </c>
-      <c r="T14" s="52">
+      <c r="W14" s="52">
         <v>36.341031196979053</v>
       </c>
-      <c r="U14" s="52">
+      <c r="X14" s="52">
         <v>38.739669421487605</v>
       </c>
-      <c r="V14" s="52">
+      <c r="Y14" s="52">
         <v>41.296626360203469</v>
       </c>
-      <c r="W14" s="52">
+      <c r="Z14" s="52">
         <v>44.022351615326826</v>
       </c>
-      <c r="X14" s="52">
+      <c r="AA14" s="52">
         <v>46.927984500231219</v>
       </c>
-      <c r="Y14" s="52">
+      <c r="AB14" s="52">
         <v>50.025399562871399</v>
       </c>
-      <c r="Z14" s="52">
+      <c r="AC14" s="52">
         <v>53.32725511389912</v>
       </c>
-      <c r="AA14" s="52">
+      <c r="AD14" s="52">
         <v>56.847044957808414</v>
       </c>
-      <c r="AB14" s="52">
+      <c r="AE14" s="52">
         <v>60.599153538521733</v>
       </c>
-      <c r="AC14" s="52">
+      <c r="AF14" s="52">
         <v>64.59891472478229</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="72">
+        <v>3.3232628398789075</v>
+      </c>
+      <c r="C15" s="72">
+        <v>3.8821752265860141</v>
+      </c>
+      <c r="D15" s="72">
+        <v>4.4410876132930506</v>
+      </c>
+      <c r="E15" s="54">
         <v>5</v>
       </c>
-      <c r="C15" s="52">
+      <c r="F15" s="52">
         <v>7.2714285714282596</v>
       </c>
-      <c r="D15" s="52">
+      <c r="G15" s="52">
         <v>9.5428571428565192</v>
       </c>
-      <c r="E15" s="52">
+      <c r="H15" s="52">
         <v>11.814285714284779</v>
       </c>
-      <c r="F15" s="52">
+      <c r="I15" s="52">
         <v>14.085714285713948</v>
       </c>
-      <c r="G15" s="52">
+      <c r="J15" s="52">
         <v>16.357142857142208</v>
       </c>
-      <c r="H15" s="52">
+      <c r="K15" s="52">
         <v>18.628571428570467</v>
       </c>
-      <c r="I15" s="54">
+      <c r="L15" s="54">
         <v>20.9</v>
       </c>
-      <c r="J15" s="52">
+      <c r="M15" s="52">
         <v>24.789999999999964</v>
       </c>
-      <c r="K15" s="52">
+      <c r="N15" s="52">
         <v>28.680000000000291</v>
       </c>
-      <c r="L15" s="52">
+      <c r="O15" s="52">
         <v>32.569999999999709</v>
       </c>
-      <c r="M15" s="52">
+      <c r="P15" s="52">
         <v>36.460000000000036</v>
       </c>
-      <c r="N15" s="52">
+      <c r="Q15" s="52">
         <v>40.350000000000364</v>
       </c>
-      <c r="O15" s="52">
+      <c r="R15" s="52">
         <v>44.239999999999782</v>
       </c>
-      <c r="P15" s="52">
+      <c r="S15" s="52">
         <v>48.130000000000109</v>
       </c>
-      <c r="Q15" s="52">
+      <c r="T15" s="52">
         <v>52.020000000000437</v>
       </c>
-      <c r="R15" s="52">
+      <c r="U15" s="52">
         <v>55.909999999999854</v>
       </c>
-      <c r="S15" s="54">
+      <c r="V15" s="54">
         <v>59.8</v>
       </c>
-      <c r="T15" s="52">
+      <c r="W15" s="52">
         <v>63.959999999999127</v>
       </c>
-      <c r="U15" s="52">
+      <c r="X15" s="52">
         <v>68.1200000000008</v>
       </c>
-      <c r="V15" s="52">
+      <c r="Y15" s="52">
         <v>72.280000000000655</v>
       </c>
-      <c r="W15" s="52">
+      <c r="Z15" s="52">
         <v>76.440000000000509</v>
       </c>
-      <c r="X15" s="52">
+      <c r="AA15" s="52">
         <v>80.600000000000364</v>
       </c>
-      <c r="Y15" s="52">
+      <c r="AB15" s="52">
         <v>84.760000000000218</v>
       </c>
-      <c r="Z15" s="52">
+      <c r="AC15" s="52">
         <v>88.920000000000073</v>
       </c>
-      <c r="AA15" s="52">
+      <c r="AD15" s="52">
         <v>93.079999999999927</v>
       </c>
-      <c r="AB15" s="52">
+      <c r="AE15" s="52">
         <v>97.239999999999782</v>
       </c>
-      <c r="AC15" s="54">
+      <c r="AF15" s="54">
         <v>101.4</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="19.5" customHeight="1"/>
-    <row r="18" spans="1:33" s="65" customFormat="1">
+    <row r="17" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:33" s="65" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="68" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:33" s="67" customFormat="1">
+    <row r="19" spans="1:33" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="55"/>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
         <v>156</v>
       </c>
@@ -54768,7 +54811,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
         <v>158</v>
       </c>
@@ -54776,7 +54819,7 @@
         <v>0.185</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="43" t="s">
         <v>159</v>
       </c>
@@ -54784,7 +54827,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="43" t="s">
         <v>160</v>
       </c>
@@ -54792,363 +54835,399 @@
         <v>0.20500000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="43">
+      <c r="B26" s="71">
+        <v>2020</v>
+      </c>
+      <c r="C26" s="71">
+        <v>2021</v>
+      </c>
+      <c r="D26" s="71">
+        <v>2022</v>
+      </c>
+      <c r="E26" s="43">
         <v>2023</v>
       </c>
-      <c r="C26" s="43">
+      <c r="F26" s="43">
         <v>2024</v>
       </c>
-      <c r="D26" s="43">
+      <c r="G26" s="43">
         <v>2025</v>
       </c>
-      <c r="E26" s="43">
+      <c r="H26" s="43">
         <v>2026</v>
       </c>
-      <c r="F26" s="43">
+      <c r="I26" s="43">
         <v>2027</v>
       </c>
-      <c r="G26" s="43">
+      <c r="J26" s="43">
         <v>2028</v>
       </c>
-      <c r="H26" s="43">
+      <c r="K26" s="43">
         <v>2029</v>
       </c>
-      <c r="I26" s="43">
+      <c r="L26" s="43">
         <v>2030</v>
       </c>
-      <c r="J26" s="43">
+      <c r="M26" s="43">
         <v>2031</v>
       </c>
-      <c r="K26" s="43">
+      <c r="N26" s="43">
         <v>2032</v>
       </c>
-      <c r="L26" s="43">
+      <c r="O26" s="43">
         <v>2033</v>
       </c>
-      <c r="M26" s="43">
+      <c r="P26" s="43">
         <v>2034</v>
       </c>
-      <c r="N26" s="43">
+      <c r="Q26" s="43">
         <v>2035</v>
       </c>
-      <c r="O26" s="43">
+      <c r="R26" s="43">
         <v>2036</v>
       </c>
-      <c r="P26" s="43">
+      <c r="S26" s="43">
         <v>2037</v>
       </c>
-      <c r="Q26" s="43">
+      <c r="T26" s="43">
         <v>2038</v>
       </c>
-      <c r="R26" s="43">
+      <c r="U26" s="43">
         <v>2039</v>
       </c>
-      <c r="S26" s="43">
+      <c r="V26" s="43">
         <v>2040</v>
       </c>
-      <c r="T26" s="43">
+      <c r="W26" s="43">
         <v>2041</v>
       </c>
-      <c r="U26" s="43">
+      <c r="X26" s="43">
         <v>2042</v>
       </c>
-      <c r="V26" s="43">
+      <c r="Y26" s="43">
         <v>2043</v>
       </c>
-      <c r="W26" s="43">
+      <c r="Z26" s="43">
         <v>2044</v>
       </c>
-      <c r="X26" s="43">
+      <c r="AA26" s="43">
         <v>2045</v>
       </c>
-      <c r="Y26" s="43">
+      <c r="AB26" s="43">
         <v>2046</v>
       </c>
-      <c r="Z26" s="43">
+      <c r="AC26" s="43">
         <v>2047</v>
       </c>
-      <c r="AA26" s="43">
+      <c r="AD26" s="43">
         <v>2048</v>
       </c>
-      <c r="AB26" s="43">
+      <c r="AE26" s="43">
         <v>2049</v>
       </c>
-      <c r="AC26" s="43">
+      <c r="AF26" s="43">
         <v>2050</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="B27" s="56">
+      <c r="B27" s="73">
+        <v>0.61480362537759792</v>
+      </c>
+      <c r="C27" s="73">
+        <v>0.71820241691841258</v>
+      </c>
+      <c r="D27" s="73">
+        <v>0.82160120845921436</v>
+      </c>
+      <c r="E27" s="56">
         <v>0.92500000000000004</v>
       </c>
-      <c r="C27" s="56">
+      <c r="F27" s="56">
         <v>0.97124999999999995</v>
       </c>
-      <c r="D27" s="56">
+      <c r="G27" s="56">
         <v>1.0174999999999998</v>
       </c>
-      <c r="E27" s="56">
+      <c r="H27" s="56">
         <v>1.1007500000000083</v>
       </c>
-      <c r="F27" s="56">
+      <c r="I27" s="56">
         <v>1.1839999999999999</v>
       </c>
-      <c r="G27" s="56">
+      <c r="J27" s="56">
         <v>1.2826666666666779</v>
       </c>
-      <c r="H27" s="56">
+      <c r="K27" s="56">
         <v>1.3813333333333389</v>
       </c>
-      <c r="I27" s="56">
+      <c r="L27" s="56">
         <v>1.48</v>
       </c>
-      <c r="J27" s="56">
+      <c r="M27" s="56">
         <v>1.6187499999999999</v>
       </c>
-      <c r="K27" s="56">
+      <c r="N27" s="56">
         <v>1.7575000000000001</v>
       </c>
-      <c r="L27" s="56">
+      <c r="O27" s="56">
         <v>1.89625</v>
       </c>
-      <c r="M27" s="56">
+      <c r="P27" s="56">
         <v>2.0350000000000001</v>
       </c>
-      <c r="N27" s="56">
+      <c r="Q27" s="56">
         <v>2.1737500000000001</v>
       </c>
-      <c r="O27" s="56">
+      <c r="R27" s="56">
         <v>2.3124999999999996</v>
       </c>
-      <c r="P27" s="56">
+      <c r="S27" s="56">
         <v>2.4975000000000001</v>
       </c>
-      <c r="Q27" s="56">
+      <c r="T27" s="56">
         <v>2.6825000000000001</v>
       </c>
-      <c r="R27" s="56">
+      <c r="U27" s="56">
         <v>2.8891409190276618</v>
       </c>
-      <c r="S27" s="56">
+      <c r="V27" s="56">
         <v>3.1117000000000012</v>
       </c>
-      <c r="T27" s="56">
+      <c r="W27" s="56">
         <v>3.3514034660720893</v>
       </c>
-      <c r="U27" s="56">
+      <c r="X27" s="56">
         <v>3.6095720000000031</v>
       </c>
-      <c r="V27" s="56">
+      <c r="Y27" s="56">
         <v>3.8876280206436249</v>
       </c>
-      <c r="W27" s="56">
+      <c r="Z27" s="56">
         <v>4.1871035200000044</v>
       </c>
-      <c r="X27" s="56">
+      <c r="AA27" s="56">
         <v>4.5096485039466065</v>
       </c>
-      <c r="Y27" s="56">
+      <c r="AB27" s="56">
         <v>4.8570400832000074</v>
       </c>
-      <c r="Z27" s="56">
+      <c r="AC27" s="56">
         <v>5.2311922645780653</v>
       </c>
-      <c r="AA27" s="56">
+      <c r="AD27" s="56">
         <v>5.6341664965120106</v>
       </c>
-      <c r="AB27" s="56">
+      <c r="AE27" s="56">
         <v>6.0681830269105586</v>
       </c>
-      <c r="AC27" s="56">
+      <c r="AF27" s="56">
         <v>6.5356331359539341</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="56">
+      <c r="B28" s="73">
+        <v>2.0271903323261333</v>
+      </c>
+      <c r="C28" s="73">
+        <v>2.3681268882174686</v>
+      </c>
+      <c r="D28" s="73">
+        <v>2.7090634441087609</v>
+      </c>
+      <c r="E28" s="56">
         <v>3.05</v>
       </c>
-      <c r="C28" s="56">
+      <c r="F28" s="56">
         <v>3.2025000000000001</v>
       </c>
-      <c r="D28" s="56">
+      <c r="G28" s="56">
         <v>3.3549999999999995</v>
       </c>
-      <c r="E28" s="56">
+      <c r="H28" s="56">
         <v>3.6295000000000277</v>
       </c>
-      <c r="F28" s="56">
+      <c r="I28" s="56">
         <v>3.9039999999999999</v>
       </c>
-      <c r="G28" s="56">
+      <c r="J28" s="56">
         <v>4.2293333333333702</v>
       </c>
-      <c r="H28" s="56">
+      <c r="K28" s="56">
         <v>4.5546666666666846</v>
       </c>
-      <c r="I28" s="56">
+      <c r="L28" s="56">
         <v>4.88</v>
       </c>
-      <c r="J28" s="56">
+      <c r="M28" s="56">
         <v>5.3374999999999995</v>
       </c>
-      <c r="K28" s="56">
+      <c r="N28" s="56">
         <v>5.7949999999999999</v>
       </c>
-      <c r="L28" s="56">
+      <c r="O28" s="56">
         <v>6.2524999999999995</v>
       </c>
-      <c r="M28" s="56">
+      <c r="P28" s="56">
         <v>6.71</v>
       </c>
-      <c r="N28" s="56">
+      <c r="Q28" s="56">
         <v>7.1674999999999995</v>
       </c>
-      <c r="O28" s="56">
+      <c r="R28" s="56">
         <v>7.6249999999999991</v>
       </c>
-      <c r="P28" s="56">
+      <c r="S28" s="56">
         <v>8.2349999999999994</v>
       </c>
-      <c r="Q28" s="56">
+      <c r="T28" s="56">
         <v>8.8450000000000006</v>
       </c>
-      <c r="R28" s="56">
+      <c r="U28" s="56">
         <v>9.5263565438209401</v>
       </c>
-      <c r="S28" s="56">
+      <c r="V28" s="56">
         <v>10.260200000000005</v>
       </c>
-      <c r="T28" s="56">
+      <c r="W28" s="56">
         <v>11.050573590832295</v>
       </c>
-      <c r="U28" s="56">
+      <c r="X28" s="56">
         <v>11.90183200000001</v>
       </c>
-      <c r="V28" s="56">
+      <c r="Y28" s="56">
         <v>12.818665365365467</v>
       </c>
-      <c r="W28" s="56">
+      <c r="Z28" s="56">
         <v>13.806125120000015</v>
       </c>
-      <c r="X28" s="56">
+      <c r="AA28" s="56">
         <v>14.869651823823947</v>
       </c>
-      <c r="Y28" s="56">
+      <c r="AB28" s="56">
         <v>16.015105139200024</v>
       </c>
-      <c r="Z28" s="56">
+      <c r="AC28" s="56">
         <v>17.248796115635784</v>
       </c>
-      <c r="AA28" s="56">
+      <c r="AD28" s="56">
         <v>18.577521961472033</v>
       </c>
-      <c r="AB28" s="56">
+      <c r="AE28" s="56">
         <v>20.008603494137517</v>
       </c>
-      <c r="AC28" s="56">
+      <c r="AF28" s="56">
         <v>21.549925475307568</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="B29" s="56">
+      <c r="B29" s="73">
+        <v>0.68126888217517623</v>
+      </c>
+      <c r="C29" s="73">
+        <v>0.79584592145013322</v>
+      </c>
+      <c r="D29" s="73">
+        <v>0.91042296072507567</v>
+      </c>
+      <c r="E29" s="56">
         <v>1.0250000000000004</v>
       </c>
-      <c r="C29" s="56">
+      <c r="F29" s="56">
         <v>1.0762500000000004</v>
       </c>
-      <c r="D29" s="56">
+      <c r="G29" s="56">
         <v>1.1275000000000002</v>
       </c>
-      <c r="E29" s="56">
+      <c r="H29" s="56">
         <v>1.2197500000000097</v>
       </c>
-      <c r="F29" s="56">
+      <c r="I29" s="56">
         <v>1.3120000000000005</v>
       </c>
-      <c r="G29" s="56">
+      <c r="J29" s="56">
         <v>1.4213333333333462</v>
       </c>
-      <c r="H29" s="56">
+      <c r="K29" s="56">
         <v>1.5306666666666735</v>
       </c>
-      <c r="I29" s="56">
+      <c r="L29" s="56">
         <v>1.6400000000000006</v>
       </c>
-      <c r="J29" s="56">
+      <c r="M29" s="56">
         <v>1.7937500000000006</v>
       </c>
-      <c r="K29" s="56">
+      <c r="N29" s="56">
         <v>1.9475000000000007</v>
       </c>
-      <c r="L29" s="56">
+      <c r="O29" s="56">
         <v>2.1012500000000007</v>
       </c>
-      <c r="M29" s="56">
+      <c r="P29" s="56">
         <v>2.2550000000000008</v>
       </c>
-      <c r="N29" s="56">
+      <c r="Q29" s="56">
         <v>2.4087500000000008</v>
       </c>
-      <c r="O29" s="56">
+      <c r="R29" s="56">
         <v>2.5625000000000004</v>
       </c>
-      <c r="P29" s="56">
+      <c r="S29" s="56">
         <v>2.767500000000001</v>
       </c>
-      <c r="Q29" s="56">
+      <c r="T29" s="56">
         <v>2.972500000000001</v>
       </c>
-      <c r="R29" s="56">
+      <c r="U29" s="56">
         <v>3.2014804778414643</v>
       </c>
-      <c r="S29" s="56">
+      <c r="V29" s="56">
         <v>3.4481000000000028</v>
       </c>
-      <c r="T29" s="56">
+      <c r="W29" s="56">
         <v>3.7137173542961004</v>
       </c>
-      <c r="U29" s="56">
+      <c r="X29" s="56">
         <v>3.9997960000000048</v>
       </c>
-      <c r="V29" s="56">
+      <c r="Y29" s="56">
         <v>4.3079121309834782</v>
       </c>
-      <c r="W29" s="56">
+      <c r="Z29" s="56">
         <v>4.639763360000007</v>
       </c>
-      <c r="X29" s="56">
+      <c r="AA29" s="56">
         <v>4.9971780719408363</v>
       </c>
-      <c r="Y29" s="56">
+      <c r="AB29" s="56">
         <v>5.3821254976000104</v>
       </c>
-      <c r="Z29" s="56">
+      <c r="AC29" s="56">
         <v>5.7967265634513723</v>
       </c>
-      <c r="AA29" s="56">
+      <c r="AD29" s="56">
         <v>6.2432655772160137</v>
       </c>
-      <c r="AB29" s="56">
+      <c r="AE29" s="56">
         <v>6.7242028136035943</v>
       </c>
-      <c r="AC29" s="56">
+      <c r="AF29" s="56">
         <v>7.2421880695705783</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="70" t="s">
         <v>168</v>
       </c>
@@ -55249,406 +55328,418 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
         <v>158</v>
       </c>
       <c r="B33" s="59">
         <f t="shared" ref="B33:D35" si="0">C33</f>
+        <v>2097.7972719031677</v>
+      </c>
+      <c r="C33" s="57">
+        <f>B27*About!$B$31</f>
+        <v>2097.7972719031677</v>
+      </c>
+      <c r="D33" s="57">
+        <f>C27*About!$B$31</f>
+        <v>2450.6086312688262</v>
+      </c>
+      <c r="E33" s="57">
+        <f>D27*About!$B$31</f>
+        <v>2803.4199906344406</v>
+      </c>
+      <c r="F33" s="57">
+        <f>E27*About!$B$31</f>
         <v>3156.23135</v>
       </c>
-      <c r="C33" s="59">
-        <f t="shared" si="0"/>
-        <v>3156.23135</v>
-      </c>
-      <c r="D33" s="59">
-        <f t="shared" si="0"/>
-        <v>3156.23135</v>
-      </c>
-      <c r="E33" s="59">
-        <f>F33</f>
-        <v>3156.23135</v>
-      </c>
-      <c r="F33" s="57">
-        <f>B27*About!$B$31</f>
-        <v>3156.23135</v>
-      </c>
       <c r="G33" s="57">
-        <f>C27*About!$B$31</f>
+        <f>F27*About!$B$31</f>
         <v>3314.0429174999995</v>
       </c>
       <c r="H33" s="57">
-        <f>D27*About!$B$31</f>
+        <f>G27*About!$B$31</f>
         <v>3471.8544849999994</v>
       </c>
       <c r="I33" s="57">
-        <f>E27*About!$B$31</f>
+        <f>H27*About!$B$31</f>
         <v>3755.9153065000282</v>
       </c>
       <c r="J33" s="57">
-        <f>F27*About!$B$31</f>
+        <f>I27*About!$B$31</f>
         <v>4039.9761279999998</v>
       </c>
       <c r="K33" s="57">
-        <f>G27*About!$B$31</f>
+        <f>J27*About!$B$31</f>
         <v>4376.6408053333716</v>
       </c>
       <c r="L33" s="57">
-        <f>H27*About!$B$31</f>
+        <f>K27*About!$B$31</f>
         <v>4713.3054826666848</v>
       </c>
       <c r="M33" s="57">
-        <f>I27*About!$B$31</f>
+        <f>L27*About!$B$31</f>
         <v>5049.9701599999999</v>
       </c>
       <c r="N33" s="57">
-        <f>J27*About!$B$31</f>
+        <f>M27*About!$B$31</f>
         <v>5523.4048624999996</v>
       </c>
       <c r="O33" s="57">
-        <f>K27*About!$B$31</f>
+        <f>N27*About!$B$31</f>
         <v>5996.8395650000002</v>
       </c>
       <c r="P33" s="57">
-        <f>L27*About!$B$31</f>
+        <f>O27*About!$B$31</f>
         <v>6470.2742675</v>
       </c>
       <c r="Q33" s="57">
-        <f>M27*About!$B$31</f>
+        <f>P27*About!$B$31</f>
         <v>6943.7089699999997</v>
       </c>
       <c r="R33" s="57">
-        <f>N27*About!$B$31</f>
+        <f>Q27*About!$B$31</f>
         <v>7417.1436724999994</v>
       </c>
       <c r="S33" s="57">
-        <f>O27*About!$B$31</f>
+        <f>R27*About!$B$31</f>
         <v>7890.5783749999982</v>
       </c>
       <c r="T33" s="57">
-        <f>P27*About!$B$31</f>
+        <f>S27*About!$B$31</f>
         <v>8521.8246450000006</v>
       </c>
       <c r="U33" s="57">
-        <f>Q27*About!$B$31</f>
+        <f>T27*About!$B$31</f>
         <v>9153.0709150000002</v>
       </c>
       <c r="V33" s="57">
-        <f>R27*About!$B$31</f>
+        <f>U27*About!$B$31</f>
         <v>9858.1590737328843</v>
       </c>
       <c r="W33" s="57">
-        <f>S27*About!$B$31</f>
+        <f>V27*About!$B$31</f>
         <v>10617.562261400004</v>
       </c>
       <c r="X33" s="57">
-        <f>T27*About!$B$31</f>
+        <f>W27*About!$B$31</f>
         <v>11435.464525530151</v>
       </c>
       <c r="Y33" s="57">
-        <f>U27*About!$B$31</f>
+        <f>X27*About!$B$31</f>
         <v>12316.372223224011</v>
       </c>
       <c r="Z33" s="57">
-        <f>V27*About!$B$31</f>
+        <f>Y27*About!$B$31</f>
         <v>13265.138849614979</v>
       </c>
       <c r="AA33" s="57">
-        <f>W27*About!$B$31</f>
+        <f>Z27*About!$B$31</f>
         <v>14286.991778939855</v>
       </c>
       <c r="AB33" s="57">
-        <f>X27*About!$B$31</f>
+        <f>AA27*About!$B$31</f>
         <v>15387.561065553382</v>
       </c>
       <c r="AC33" s="57">
-        <f>Y27*About!$B$31</f>
+        <f>AB27*About!$B$31</f>
         <v>16572.910463570239</v>
       </c>
       <c r="AD33" s="57">
-        <f>Z27*About!$B$31</f>
+        <f>AC27*About!$B$31</f>
         <v>17849.570836041927</v>
       </c>
       <c r="AE33" s="57">
-        <f>AA27*About!$B$31</f>
+        <f>AD27*About!$B$31</f>
         <v>19224.576137741486</v>
       </c>
       <c r="AF33" s="57">
-        <f>AB27*About!$B$31</f>
+        <f>AE27*About!$B$31</f>
         <v>20705.502169808646</v>
       </c>
       <c r="AG33" s="57">
-        <f>AC27*About!$B$31</f>
+        <f>AF27*About!$B$31</f>
         <v>22300.508319780129</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="43" t="s">
         <v>159</v>
       </c>
       <c r="B34" s="59">
         <f t="shared" si="0"/>
+        <v>6917.0612749239572</v>
+      </c>
+      <c r="C34" s="57">
+        <f>B28*About!$B$31</f>
+        <v>6917.0612749239572</v>
+      </c>
+      <c r="D34" s="57">
+        <f>C28*About!$B$31</f>
+        <v>8080.3852166161296</v>
+      </c>
+      <c r="E34" s="57">
+        <f>D28*About!$B$31</f>
+        <v>9243.7091583081547</v>
+      </c>
+      <c r="F34" s="57">
+        <f>E28*About!$B$31</f>
         <v>10407.033099999999</v>
       </c>
-      <c r="C34" s="59">
-        <f t="shared" si="0"/>
-        <v>10407.033099999999</v>
-      </c>
-      <c r="D34" s="59">
-        <f t="shared" si="0"/>
-        <v>10407.033099999999</v>
-      </c>
-      <c r="E34" s="59">
-        <f t="shared" ref="E34:E35" si="1">F34</f>
-        <v>10407.033099999999</v>
-      </c>
-      <c r="F34" s="57">
-        <f>B28*About!$B$31</f>
-        <v>10407.033099999999</v>
-      </c>
       <c r="G34" s="57">
-        <f>C28*About!$B$31</f>
+        <f>F28*About!$B$31</f>
         <v>10927.384754999999</v>
       </c>
       <c r="H34" s="57">
-        <f>D28*About!$B$31</f>
+        <f>G28*About!$B$31</f>
         <v>11447.736409999998</v>
       </c>
       <c r="I34" s="57">
-        <f>E28*About!$B$31</f>
+        <f>H28*About!$B$31</f>
         <v>12384.369389000094</v>
       </c>
       <c r="J34" s="57">
-        <f>F28*About!$B$31</f>
+        <f>I28*About!$B$31</f>
         <v>13321.002367999999</v>
       </c>
       <c r="K34" s="57">
-        <f>G28*About!$B$31</f>
+        <f>J28*About!$B$31</f>
         <v>14431.085898666792</v>
       </c>
       <c r="L34" s="57">
-        <f>H28*About!$B$31</f>
+        <f>K28*About!$B$31</f>
         <v>15541.169429333393</v>
       </c>
       <c r="M34" s="57">
-        <f>I28*About!$B$31</f>
+        <f>L28*About!$B$31</f>
         <v>16651.252959999998</v>
       </c>
       <c r="N34" s="57">
-        <f>J28*About!$B$31</f>
+        <f>M28*About!$B$31</f>
         <v>18212.307924999997</v>
       </c>
       <c r="O34" s="57">
-        <f>K28*About!$B$31</f>
+        <f>N28*About!$B$31</f>
         <v>19773.36289</v>
       </c>
       <c r="P34" s="57">
-        <f>L28*About!$B$31</f>
+        <f>O28*About!$B$31</f>
         <v>21334.417854999996</v>
       </c>
       <c r="Q34" s="57">
-        <f>M28*About!$B$31</f>
+        <f>P28*About!$B$31</f>
         <v>22895.472819999999</v>
       </c>
       <c r="R34" s="57">
-        <f>N28*About!$B$31</f>
+        <f>Q28*About!$B$31</f>
         <v>24456.527784999998</v>
       </c>
       <c r="S34" s="57">
-        <f>O28*About!$B$31</f>
+        <f>R28*About!$B$31</f>
         <v>26017.582749999994</v>
       </c>
       <c r="T34" s="57">
-        <f>P28*About!$B$31</f>
+        <f>S28*About!$B$31</f>
         <v>28098.989369999996</v>
       </c>
       <c r="U34" s="57">
-        <f>Q28*About!$B$31</f>
+        <f>T28*About!$B$31</f>
         <v>30180.395990000001</v>
       </c>
       <c r="V34" s="57">
-        <f>R28*About!$B$31</f>
+        <f>U28*About!$B$31</f>
         <v>32505.281270146268</v>
       </c>
       <c r="W34" s="57">
-        <f>S28*About!$B$31</f>
+        <f>V28*About!$B$31</f>
         <v>35009.259348400017</v>
       </c>
       <c r="X34" s="57">
-        <f>T28*About!$B$31</f>
+        <f>W28*About!$B$31</f>
         <v>37706.126273369686</v>
       </c>
       <c r="Y34" s="57">
-        <f>U28*About!$B$31</f>
+        <f>X28*About!$B$31</f>
         <v>40610.740844144028</v>
       </c>
       <c r="Z34" s="57">
-        <f>V28*About!$B$31</f>
+        <f>Y28*About!$B$31</f>
         <v>43739.10647710885</v>
       </c>
       <c r="AA34" s="57">
-        <f>W28*About!$B$31</f>
+        <f>Z28*About!$B$31</f>
         <v>47108.459379207088</v>
       </c>
       <c r="AB34" s="57">
-        <f>X28*About!$B$31</f>
+        <f>AA28*About!$B$31</f>
         <v>50737.363513446289</v>
       </c>
       <c r="AC34" s="57">
-        <f>Y28*About!$B$31</f>
+        <f>AB28*About!$B$31</f>
         <v>54645.812879880243</v>
       </c>
       <c r="AD34" s="57">
-        <f>Z28*About!$B$31</f>
+        <f>AC28*About!$B$31</f>
         <v>58855.341675597716</v>
       </c>
       <c r="AE34" s="57">
-        <f>AA28*About!$B$31</f>
+        <f>AD28*About!$B$31</f>
         <v>63389.142940661106</v>
       </c>
       <c r="AF34" s="57">
-        <f>AB28*About!$B$31</f>
+        <f>AE28*About!$B$31</f>
         <v>68272.196343693373</v>
       </c>
       <c r="AG34" s="57">
-        <f>AC28*About!$B$31</f>
+        <f>AF28*About!$B$31</f>
         <v>73531.405811166915</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
         <v>160</v>
       </c>
       <c r="B35" s="59">
         <f t="shared" si="0"/>
+        <v>2324.5861661629701</v>
+      </c>
+      <c r="C35" s="57">
+        <f>B29*About!$B$31</f>
+        <v>2324.5861661629701</v>
+      </c>
+      <c r="D35" s="57">
+        <f>C29*About!$B$31</f>
+        <v>2715.5392941087002</v>
+      </c>
+      <c r="E35" s="57">
+        <f>D29*About!$B$31</f>
+        <v>3106.4924220543808</v>
+      </c>
+      <c r="F35" s="57">
+        <f>E29*About!$B$31</f>
         <v>3497.4455500000008</v>
       </c>
-      <c r="C35" s="59">
-        <f t="shared" si="0"/>
-        <v>3497.4455500000008</v>
-      </c>
-      <c r="D35" s="59">
-        <f t="shared" si="0"/>
-        <v>3497.4455500000008</v>
-      </c>
-      <c r="E35" s="59">
+      <c r="G35" s="57">
+        <f>F29*About!$B$31</f>
+        <v>3672.3178275000009</v>
+      </c>
+      <c r="H35" s="57">
+        <f>G29*About!$B$31</f>
+        <v>3847.1901050000006</v>
+      </c>
+      <c r="I35" s="57">
+        <f>H29*About!$B$31</f>
+        <v>4161.9602045000329</v>
+      </c>
+      <c r="J35" s="57">
+        <f>I29*About!$B$31</f>
+        <v>4476.7303040000015</v>
+      </c>
+      <c r="K35" s="57">
+        <f>J29*About!$B$31</f>
+        <v>4849.7911626667101</v>
+      </c>
+      <c r="L35" s="57">
+        <f>K29*About!$B$31</f>
+        <v>5222.8520213333568</v>
+      </c>
+      <c r="M35" s="57">
+        <f>L29*About!$B$31</f>
+        <v>5595.9128800000017</v>
+      </c>
+      <c r="N35" s="57">
+        <f>M29*About!$B$31</f>
+        <v>6120.5297125000016</v>
+      </c>
+      <c r="O35" s="57">
+        <f>N29*About!$B$31</f>
+        <v>6645.1465450000023</v>
+      </c>
+      <c r="P35" s="57">
+        <f>O29*About!$B$31</f>
+        <v>7169.7633775000022</v>
+      </c>
+      <c r="Q35" s="57">
+        <f>P29*About!$B$31</f>
+        <v>7694.3802100000021</v>
+      </c>
+      <c r="R35" s="57">
+        <f>Q29*About!$B$31</f>
+        <v>8218.9970425000029</v>
+      </c>
+      <c r="S35" s="57">
+        <f>R29*About!$B$31</f>
+        <v>8743.6138750000009</v>
+      </c>
+      <c r="T35" s="57">
+        <f>S29*About!$B$31</f>
+        <v>9443.1029850000032</v>
+      </c>
+      <c r="U35" s="57">
+        <f>T29*About!$B$31</f>
+        <v>10142.592095000004</v>
+      </c>
+      <c r="V35" s="57">
+        <f>U29*About!$B$31</f>
+        <v>10923.906000622928</v>
+      </c>
+      <c r="W35" s="57">
+        <f>V29*About!$B$31</f>
+        <v>11765.406830200009</v>
+      </c>
+      <c r="X35" s="57">
+        <f>W29*About!$B$31</f>
+        <v>12671.730960722603</v>
+      </c>
+      <c r="Y35" s="57">
+        <f>X29*About!$B$31</f>
+        <v>13647.871923032015</v>
+      </c>
+      <c r="Z35" s="57">
+        <f>Y29*About!$B$31</f>
+        <v>14699.207914438226</v>
+      </c>
+      <c r="AA35" s="57">
+        <f>Z29*About!$B$31</f>
+        <v>15831.531430717143</v>
+      </c>
+      <c r="AB35" s="57">
+        <f>AA29*About!$B$31</f>
+        <v>17051.081180748348</v>
+      </c>
+      <c r="AC35" s="57">
+        <f>AB29*About!$B$31</f>
+        <v>18364.576459631895</v>
+      </c>
+      <c r="AD35" s="57">
+        <f>AC29*About!$B$31</f>
+        <v>19779.254169668093</v>
+      </c>
+      <c r="AE35" s="57">
+        <f>AD29*About!$B$31</f>
+        <v>21302.908693173002</v>
+      </c>
+      <c r="AF35" s="57">
+        <f>AE29*About!$B$31</f>
+        <v>22943.934836814995</v>
+      </c>
+      <c r="AG35" s="57">
+        <f>AF29*About!$B$31</f>
+        <v>24711.374084080689</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="C36" s="58">
+        <f t="shared" ref="C36:E36" si="1">SUM(C33:C35)</f>
+        <v>11339.444712990095</v>
+      </c>
+      <c r="D36" s="58">
         <f t="shared" si="1"/>
-        <v>3497.4455500000008</v>
-      </c>
-      <c r="F35" s="57">
-        <f>B29*About!$B$31</f>
-        <v>3497.4455500000008</v>
-      </c>
-      <c r="G35" s="57">
-        <f>C29*About!$B$31</f>
-        <v>3672.3178275000009</v>
-      </c>
-      <c r="H35" s="57">
-        <f>D29*About!$B$31</f>
-        <v>3847.1901050000006</v>
-      </c>
-      <c r="I35" s="57">
-        <f>E29*About!$B$31</f>
-        <v>4161.9602045000329</v>
-      </c>
-      <c r="J35" s="57">
-        <f>F29*About!$B$31</f>
-        <v>4476.7303040000015</v>
-      </c>
-      <c r="K35" s="57">
-        <f>G29*About!$B$31</f>
-        <v>4849.7911626667101</v>
-      </c>
-      <c r="L35" s="57">
-        <f>H29*About!$B$31</f>
-        <v>5222.8520213333568</v>
-      </c>
-      <c r="M35" s="57">
-        <f>I29*About!$B$31</f>
-        <v>5595.9128800000017</v>
-      </c>
-      <c r="N35" s="57">
-        <f>J29*About!$B$31</f>
-        <v>6120.5297125000016</v>
-      </c>
-      <c r="O35" s="57">
-        <f>K29*About!$B$31</f>
-        <v>6645.1465450000023</v>
-      </c>
-      <c r="P35" s="57">
-        <f>L29*About!$B$31</f>
-        <v>7169.7633775000022</v>
-      </c>
-      <c r="Q35" s="57">
-        <f>M29*About!$B$31</f>
-        <v>7694.3802100000021</v>
-      </c>
-      <c r="R35" s="57">
-        <f>N29*About!$B$31</f>
-        <v>8218.9970425000029</v>
-      </c>
-      <c r="S35" s="57">
-        <f>O29*About!$B$31</f>
-        <v>8743.6138750000009</v>
-      </c>
-      <c r="T35" s="57">
-        <f>P29*About!$B$31</f>
-        <v>9443.1029850000032</v>
-      </c>
-      <c r="U35" s="57">
-        <f>Q29*About!$B$31</f>
-        <v>10142.592095000004</v>
-      </c>
-      <c r="V35" s="57">
-        <f>R29*About!$B$31</f>
-        <v>10923.906000622928</v>
-      </c>
-      <c r="W35" s="57">
-        <f>S29*About!$B$31</f>
-        <v>11765.406830200009</v>
-      </c>
-      <c r="X35" s="57">
-        <f>T29*About!$B$31</f>
-        <v>12671.730960722603</v>
-      </c>
-      <c r="Y35" s="57">
-        <f>U29*About!$B$31</f>
-        <v>13647.871923032015</v>
-      </c>
-      <c r="Z35" s="57">
-        <f>V29*About!$B$31</f>
-        <v>14699.207914438226</v>
-      </c>
-      <c r="AA35" s="57">
-        <f>W29*About!$B$31</f>
-        <v>15831.531430717143</v>
-      </c>
-      <c r="AB35" s="57">
-        <f>X29*About!$B$31</f>
-        <v>17051.081180748348</v>
-      </c>
-      <c r="AC35" s="57">
-        <f>Y29*About!$B$31</f>
-        <v>18364.576459631895</v>
-      </c>
-      <c r="AD35" s="57">
-        <f>Z29*About!$B$31</f>
-        <v>19779.254169668093</v>
-      </c>
-      <c r="AE35" s="57">
-        <f>AA29*About!$B$31</f>
-        <v>21302.908693173002</v>
-      </c>
-      <c r="AF35" s="57">
-        <f>AB29*About!$B$31</f>
-        <v>22943.934836814995</v>
-      </c>
-      <c r="AG35" s="57">
-        <f>AC29*About!$B$31</f>
-        <v>24711.374084080689</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33">
+        <v>13246.533141993656</v>
+      </c>
+      <c r="E36" s="58">
+        <f t="shared" si="1"/>
+        <v>15153.621570996977</v>
+      </c>
       <c r="F36" s="58">
         <f>SUM(F33:F35)</f>
         <v>17060.71</v>
@@ -55772,19 +55863,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF043D3D-1C43-4AD5-8A34-3CB6E2718E2E}">
   <dimension ref="A2:AG73"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="33" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="33" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>37</v>
       </c>
@@ -55885,7 +55975,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -56018,7 +56108,7 @@
         <v>84237447651332.563</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
@@ -56151,7 +56241,7 @@
         <v>141672951288.72482</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
@@ -56284,7 +56374,7 @@
         <v>264878069213172.19</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
@@ -56417,7 +56507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>7</v>
       </c>
@@ -56550,7 +56640,7 @@
         <v>80159312570864.688</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
@@ -56683,7 +56773,7 @@
         <v>5507255991053.5078</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>13</v>
       </c>
@@ -56816,7 +56906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>14</v>
       </c>
@@ -56949,7 +57039,7 @@
         <v>16056145596897.148</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
@@ -57082,7 +57172,7 @@
         <v>4915622162036.6191</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>16</v>
       </c>
@@ -57215,7 +57305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>38</v>
       </c>
@@ -57316,7 +57406,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>2</v>
       </c>
@@ -57449,7 +57539,7 @@
         <v>47698009926925.695</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>3</v>
       </c>
@@ -57582,7 +57672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>4</v>
       </c>
@@ -57715,7 +57805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>5</v>
       </c>
@@ -57848,7 +57938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>7</v>
       </c>
@@ -57981,7 +58071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>11</v>
       </c>
@@ -58114,7 +58204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>13</v>
       </c>
@@ -58247,7 +58337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>14</v>
       </c>
@@ -58380,7 +58470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>15</v>
       </c>
@@ -58513,7 +58603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>16</v>
       </c>
@@ -58646,7 +58736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>39</v>
       </c>
@@ -58747,7 +58837,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>2</v>
       </c>
@@ -58880,7 +58970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>3</v>
       </c>
@@ -59013,7 +59103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>4</v>
       </c>
@@ -59146,7 +59236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>5</v>
       </c>
@@ -59279,7 +59369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>7</v>
       </c>
@@ -59412,7 +59502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>11</v>
       </c>
@@ -59545,7 +59635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>13</v>
       </c>
@@ -59678,7 +59768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>14</v>
       </c>
@@ -59811,7 +59901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>15</v>
       </c>
@@ -59944,7 +60034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>16</v>
       </c>
@@ -60077,7 +60167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:33">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
@@ -60178,7 +60268,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:33">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>2</v>
       </c>
@@ -60311,7 +60401,7 @@
         <v>47698009926925.695</v>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>3</v>
       </c>
@@ -60444,7 +60534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:33">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>4</v>
       </c>
@@ -60577,7 +60667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:33">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>5</v>
       </c>
@@ -60710,7 +60800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:33">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>7</v>
       </c>
@@ -60843,7 +60933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:33">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>11</v>
       </c>
@@ -60976,7 +61066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:33">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
         <v>13</v>
       </c>
@@ -61109,7 +61199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:33">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="16" t="s">
         <v>14</v>
       </c>
@@ -61242,7 +61332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:33">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
         <v>15</v>
       </c>
@@ -61375,7 +61465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:33">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
         <v>16</v>
       </c>
@@ -61508,7 +61598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:33">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
         <v>46</v>
       </c>
@@ -61609,7 +61699,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="52" spans="1:33">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
         <v>2</v>
       </c>
@@ -61742,7 +61832,7 @@
         <v>109378314244044.11</v>
       </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="16" t="s">
         <v>3</v>
       </c>
@@ -61875,7 +61965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>4</v>
       </c>
@@ -62008,7 +62098,7 @@
         <v>55564771659181.594</v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>5</v>
       </c>
@@ -62141,7 +62231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
         <v>7</v>
       </c>
@@ -62274,7 +62364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
         <v>11</v>
       </c>
@@ -62407,7 +62497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
         <v>13</v>
       </c>
@@ -62540,7 +62630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
         <v>14</v>
       </c>
@@ -62673,7 +62763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
         <v>15</v>
       </c>
@@ -62806,7 +62896,7 @@
         <v>1031174169336.6079</v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
         <v>16</v>
       </c>
@@ -62939,7 +63029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
         <v>42</v>
       </c>
@@ -63040,7 +63130,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="16" t="s">
         <v>2</v>
       </c>
@@ -63173,7 +63263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:33">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
         <v>3</v>
       </c>
@@ -63306,7 +63396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:33">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
         <v>4</v>
       </c>
@@ -63439,7 +63529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
         <v>5</v>
       </c>
@@ -63572,7 +63662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="16" t="s">
         <v>7</v>
       </c>
@@ -63705,7 +63795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:33">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="16" t="s">
         <v>11</v>
       </c>
@@ -63838,7 +63928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:33">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="16" t="s">
         <v>13</v>
       </c>
@@ -63971,7 +64061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>14</v>
       </c>
@@ -64104,7 +64194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:33">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
         <v>15</v>
       </c>
@@ -64237,7 +64327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="16" t="s">
         <v>16</v>
       </c>
@@ -64374,10 +64464,4 @@
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>
-</clbl:labelList>
 </file>